--- a/public/informes-templates/REPORTE DE BOBINA DE ESTATOR-MTTO.xlsx
+++ b/public/informes-templates/REPORTE DE BOBINA DE ESTATOR-MTTO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SIP-APP\SIPAPP-ALCOINSAC\Frontend\public\informes-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E745997-DB76-48F5-A733-F10F9B8AB970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909F7CE0-9881-4CC3-AE7E-11FB53FFB0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -512,19 +512,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -548,11 +535,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -611,14 +618,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -681,15 +682,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -711,137 +703,191 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1332,472 +1378,472 @@
     <col min="70" max="70" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1"/>
-    <row r="2" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC2" s="64" t="s">
+    <row r="1" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1"/>
+    <row r="2" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC2" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AP2" s="62"/>
-      <c r="AQ2" s="62"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="62"/>
-      <c r="AT2" s="62"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="62"/>
-      <c r="AW2" s="62"/>
-      <c r="AX2" s="62"/>
-      <c r="AY2" s="62"/>
-      <c r="AZ2" s="62"/>
-      <c r="BA2" s="62"/>
-      <c r="BB2" s="62"/>
-      <c r="BC2" s="62"/>
-      <c r="BD2" s="62"/>
-    </row>
-    <row r="3" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC3" s="64" t="s">
+      <c r="AD2" s="101"/>
+      <c r="AE2" s="101"/>
+      <c r="AF2" s="101"/>
+      <c r="AG2" s="101"/>
+      <c r="AH2" s="101"/>
+      <c r="AI2" s="101"/>
+      <c r="AJ2" s="101"/>
+      <c r="AK2" s="101"/>
+      <c r="AL2" s="101"/>
+      <c r="AM2" s="101"/>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="57"/>
+      <c r="AR2" s="57"/>
+      <c r="AS2" s="57"/>
+      <c r="AT2" s="57"/>
+      <c r="AU2" s="57"/>
+      <c r="AV2" s="57"/>
+      <c r="AW2" s="57"/>
+      <c r="AX2" s="57"/>
+      <c r="AY2" s="57"/>
+      <c r="AZ2" s="57"/>
+      <c r="BA2" s="57"/>
+      <c r="BB2" s="57"/>
+      <c r="BC2" s="57"/>
+      <c r="BD2" s="57"/>
+    </row>
+    <row r="3" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC3" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="AD3" s="64"/>
-      <c r="AE3" s="64"/>
-      <c r="AF3" s="64"/>
-      <c r="AG3" s="64"/>
-      <c r="AH3" s="64"/>
-      <c r="AI3" s="64"/>
-      <c r="AJ3" s="64"/>
-      <c r="AK3" s="64"/>
-      <c r="AL3" s="64"/>
-      <c r="AM3" s="64"/>
-      <c r="AP3" s="62"/>
-      <c r="AQ3" s="62"/>
-      <c r="AR3" s="62"/>
-      <c r="AS3" s="62"/>
-      <c r="AT3" s="62"/>
-      <c r="AU3" s="62"/>
-      <c r="AV3" s="62"/>
-      <c r="AW3" s="62"/>
-      <c r="AX3" s="62"/>
-      <c r="AY3" s="62"/>
-      <c r="AZ3" s="62"/>
-      <c r="BA3" s="62"/>
-      <c r="BB3" s="62"/>
-      <c r="BC3" s="62"/>
-      <c r="BD3" s="62"/>
-    </row>
-    <row r="4" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC4" s="64" t="s">
+      <c r="AD3" s="101"/>
+      <c r="AE3" s="101"/>
+      <c r="AF3" s="101"/>
+      <c r="AG3" s="101"/>
+      <c r="AH3" s="101"/>
+      <c r="AI3" s="101"/>
+      <c r="AJ3" s="101"/>
+      <c r="AK3" s="101"/>
+      <c r="AL3" s="101"/>
+      <c r="AM3" s="101"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="57"/>
+      <c r="AZ3" s="57"/>
+      <c r="BA3" s="57"/>
+      <c r="BB3" s="57"/>
+      <c r="BC3" s="57"/>
+      <c r="BD3" s="57"/>
+    </row>
+    <row r="4" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC4" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="64"/>
-      <c r="AE4" s="64"/>
-      <c r="AF4" s="64"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="64"/>
-      <c r="AI4" s="64"/>
-      <c r="AJ4" s="64"/>
-      <c r="AK4" s="64"/>
-      <c r="AL4" s="64"/>
-      <c r="AM4" s="64"/>
-      <c r="AP4" s="62"/>
-      <c r="AQ4" s="62"/>
-      <c r="AR4" s="62"/>
-      <c r="AS4" s="62"/>
-      <c r="AT4" s="62"/>
-      <c r="AU4" s="62"/>
-      <c r="AV4" s="62"/>
-      <c r="AW4" s="62"/>
-      <c r="AX4" s="62"/>
-      <c r="AY4" s="62"/>
-      <c r="AZ4" s="62"/>
-      <c r="BA4" s="62"/>
-      <c r="BB4" s="62"/>
-      <c r="BC4" s="62"/>
-      <c r="BD4" s="62"/>
-    </row>
-    <row r="5" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC5" s="64" t="s">
+      <c r="AD4" s="101"/>
+      <c r="AE4" s="101"/>
+      <c r="AF4" s="101"/>
+      <c r="AG4" s="101"/>
+      <c r="AH4" s="101"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="101"/>
+      <c r="AL4" s="101"/>
+      <c r="AM4" s="101"/>
+      <c r="AP4" s="57"/>
+      <c r="AQ4" s="57"/>
+      <c r="AR4" s="57"/>
+      <c r="AS4" s="57"/>
+      <c r="AT4" s="57"/>
+      <c r="AU4" s="57"/>
+      <c r="AV4" s="57"/>
+      <c r="AW4" s="57"/>
+      <c r="AX4" s="57"/>
+      <c r="AY4" s="57"/>
+      <c r="AZ4" s="57"/>
+      <c r="BA4" s="57"/>
+      <c r="BB4" s="57"/>
+      <c r="BC4" s="57"/>
+      <c r="BD4" s="57"/>
+    </row>
+    <row r="5" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC5" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="64"/>
-      <c r="AE5" s="64"/>
-      <c r="AF5" s="64"/>
-      <c r="AG5" s="64"/>
-      <c r="AH5" s="64"/>
-      <c r="AI5" s="64"/>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AP5" s="62"/>
-      <c r="AQ5" s="62"/>
-      <c r="AR5" s="62"/>
-      <c r="AS5" s="62"/>
-      <c r="AT5" s="62"/>
-      <c r="AU5" s="62"/>
-      <c r="AV5" s="62"/>
-      <c r="AW5" s="62"/>
-      <c r="AX5" s="62"/>
-      <c r="AY5" s="62"/>
-      <c r="AZ5" s="62"/>
-      <c r="BA5" s="62"/>
-      <c r="BB5" s="62"/>
-      <c r="BC5" s="62"/>
-      <c r="BD5" s="62"/>
-    </row>
-    <row r="6" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC6" s="64" t="s">
+      <c r="AD5" s="101"/>
+      <c r="AE5" s="101"/>
+      <c r="AF5" s="101"/>
+      <c r="AG5" s="101"/>
+      <c r="AH5" s="101"/>
+      <c r="AI5" s="101"/>
+      <c r="AJ5" s="101"/>
+      <c r="AK5" s="101"/>
+      <c r="AL5" s="101"/>
+      <c r="AM5" s="101"/>
+      <c r="AP5" s="57"/>
+      <c r="AQ5" s="57"/>
+      <c r="AR5" s="57"/>
+      <c r="AS5" s="57"/>
+      <c r="AT5" s="57"/>
+      <c r="AU5" s="57"/>
+      <c r="AV5" s="57"/>
+      <c r="AW5" s="57"/>
+      <c r="AX5" s="57"/>
+      <c r="AY5" s="57"/>
+      <c r="AZ5" s="57"/>
+      <c r="BA5" s="57"/>
+      <c r="BB5" s="57"/>
+      <c r="BC5" s="57"/>
+      <c r="BD5" s="57"/>
+    </row>
+    <row r="6" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC6" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="AD6" s="64"/>
-      <c r="AE6" s="64"/>
-      <c r="AF6" s="64"/>
-      <c r="AG6" s="64"/>
-      <c r="AH6" s="64"/>
-      <c r="AI6" s="64"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="64"/>
-      <c r="AP6" s="62"/>
-      <c r="AQ6" s="62"/>
-      <c r="AR6" s="62"/>
-      <c r="AS6" s="62"/>
-      <c r="AT6" s="62"/>
-      <c r="AU6" s="62"/>
-      <c r="AV6" s="62"/>
-      <c r="AW6" s="62"/>
-      <c r="AX6" s="62"/>
-      <c r="AY6" s="62"/>
-      <c r="AZ6" s="62"/>
-      <c r="BA6" s="62"/>
-      <c r="BB6" s="62"/>
-      <c r="BC6" s="62"/>
-      <c r="BD6" s="62"/>
-    </row>
-    <row r="7" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1">
-      <c r="AC7" s="63"/>
-      <c r="AD7" s="63"/>
-      <c r="AE7" s="63"/>
-      <c r="AF7" s="63"/>
-      <c r="AG7" s="63"/>
-      <c r="AH7" s="63"/>
-      <c r="AI7" s="63"/>
-      <c r="AJ7" s="63"/>
-      <c r="AK7" s="63"/>
-      <c r="AL7" s="63"/>
-      <c r="AM7" s="63"/>
-      <c r="AP7" s="62"/>
-      <c r="AQ7" s="62"/>
-      <c r="AR7" s="62"/>
-      <c r="AS7" s="62"/>
-      <c r="AT7" s="62"/>
-      <c r="AU7" s="62"/>
-      <c r="AV7" s="62"/>
-      <c r="AW7" s="62"/>
-      <c r="AX7" s="62"/>
-      <c r="AY7" s="62"/>
-      <c r="AZ7" s="62"/>
-      <c r="BA7" s="62"/>
-      <c r="BB7" s="62"/>
-      <c r="BC7" s="62"/>
-      <c r="BD7" s="62"/>
-    </row>
-    <row r="8" spans="3:56" s="61" customFormat="1" ht="11.25" customHeight="1"/>
+      <c r="AD6" s="101"/>
+      <c r="AE6" s="101"/>
+      <c r="AF6" s="101"/>
+      <c r="AG6" s="101"/>
+      <c r="AH6" s="101"/>
+      <c r="AI6" s="101"/>
+      <c r="AJ6" s="101"/>
+      <c r="AK6" s="101"/>
+      <c r="AL6" s="101"/>
+      <c r="AM6" s="101"/>
+      <c r="AP6" s="57"/>
+      <c r="AQ6" s="57"/>
+      <c r="AR6" s="57"/>
+      <c r="AS6" s="57"/>
+      <c r="AT6" s="57"/>
+      <c r="AU6" s="57"/>
+      <c r="AV6" s="57"/>
+      <c r="AW6" s="57"/>
+      <c r="AX6" s="57"/>
+      <c r="AY6" s="57"/>
+      <c r="AZ6" s="57"/>
+      <c r="BA6" s="57"/>
+      <c r="BB6" s="57"/>
+      <c r="BC6" s="57"/>
+      <c r="BD6" s="57"/>
+    </row>
+    <row r="7" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1">
+      <c r="AC7" s="58"/>
+      <c r="AD7" s="58"/>
+      <c r="AE7" s="58"/>
+      <c r="AF7" s="58"/>
+      <c r="AG7" s="58"/>
+      <c r="AH7" s="58"/>
+      <c r="AI7" s="58"/>
+      <c r="AJ7" s="58"/>
+      <c r="AK7" s="58"/>
+      <c r="AL7" s="58"/>
+      <c r="AM7" s="58"/>
+      <c r="AP7" s="57"/>
+      <c r="AQ7" s="57"/>
+      <c r="AR7" s="57"/>
+      <c r="AS7" s="57"/>
+      <c r="AT7" s="57"/>
+      <c r="AU7" s="57"/>
+      <c r="AV7" s="57"/>
+      <c r="AW7" s="57"/>
+      <c r="AX7" s="57"/>
+      <c r="AY7" s="57"/>
+      <c r="AZ7" s="57"/>
+      <c r="BA7" s="57"/>
+      <c r="BB7" s="57"/>
+      <c r="BC7" s="57"/>
+      <c r="BD7" s="57"/>
+    </row>
+    <row r="8" spans="3:56" s="56" customFormat="1" ht="11.25" customHeight="1"/>
     <row r="9" spans="3:56" ht="11.25" customHeight="1">
       <c r="C9" s="2"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="65" t="s">
+      <c r="D9" s="34"/>
+      <c r="E9" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="66"/>
-      <c r="N9" s="66"/>
-      <c r="O9" s="66"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="66"/>
-      <c r="S9" s="66"/>
-      <c r="T9" s="66"/>
-      <c r="U9" s="66"/>
-      <c r="V9" s="66"/>
-      <c r="W9" s="66"/>
-      <c r="X9" s="66"/>
-      <c r="Y9" s="66"/>
-      <c r="Z9" s="66"/>
-      <c r="AA9" s="66"/>
-      <c r="AB9" s="66"/>
-      <c r="AC9" s="66"/>
-      <c r="AD9" s="66"/>
-      <c r="AE9" s="66"/>
-      <c r="AF9" s="66"/>
-      <c r="AG9" s="66"/>
-      <c r="AH9" s="66"/>
-      <c r="AI9" s="66"/>
-      <c r="AJ9" s="67"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99"/>
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="100"/>
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="34"/>
     </row>
     <row r="10" spans="3:56" ht="11.25" customHeight="1">
       <c r="C10" s="2"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="35"/>
     </row>
     <row r="11" spans="3:56" ht="11.25" customHeight="1">
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="68" t="s">
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="84"/>
+      <c r="R11" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="74"/>
-      <c r="W11" s="74"/>
-      <c r="X11" s="74"/>
-      <c r="Y11" s="74"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="74"/>
-      <c r="AC11" s="74"/>
-      <c r="AD11" s="74"/>
-      <c r="AE11" s="74"/>
-      <c r="AF11" s="68" t="s">
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="81"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="73"/>
-      <c r="AJ11" s="73"/>
-      <c r="AK11" s="73"/>
-      <c r="AL11" s="73"/>
+      <c r="AG11" s="81"/>
+      <c r="AH11" s="81"/>
+      <c r="AI11" s="97"/>
+      <c r="AJ11" s="97"/>
+      <c r="AK11" s="97"/>
+      <c r="AL11" s="97"/>
     </row>
     <row r="12" spans="3:56" ht="11.25" customHeight="1">
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="68" t="s">
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="68"/>
-      <c r="T12" s="68"/>
-      <c r="U12" s="68"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="74"/>
-      <c r="X12" s="74"/>
-      <c r="Y12" s="74"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="74"/>
-      <c r="AB12" s="74"/>
-      <c r="AC12" s="74"/>
-      <c r="AD12" s="74"/>
-      <c r="AE12" s="74"/>
-      <c r="AF12" s="69" t="s">
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="85"/>
+      <c r="X12" s="85"/>
+      <c r="Y12" s="85"/>
+      <c r="Z12" s="85"/>
+      <c r="AA12" s="85"/>
+      <c r="AB12" s="85"/>
+      <c r="AC12" s="85"/>
+      <c r="AD12" s="85"/>
+      <c r="AE12" s="85"/>
+      <c r="AF12" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="AG12" s="69"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="75"/>
-      <c r="AJ12" s="75"/>
-      <c r="AK12" s="75"/>
-      <c r="AL12" s="75"/>
+      <c r="AG12" s="86"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="65"/>
+      <c r="AJ12" s="65"/>
+      <c r="AK12" s="65"/>
+      <c r="AL12" s="65"/>
     </row>
     <row r="13" spans="3:56" ht="11.25" customHeight="1">
       <c r="C13" s="2"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="33"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="33"/>
-      <c r="AK13" s="33"/>
-      <c r="AL13" s="33"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
     </row>
     <row r="14" spans="3:56" ht="11.25" customHeight="1">
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="80"/>
-      <c r="R14" s="80"/>
-      <c r="S14" s="80"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="79" t="s">
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="88"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="V14" s="80"/>
-      <c r="W14" s="80"/>
-      <c r="X14" s="80"/>
-      <c r="Y14" s="80"/>
-      <c r="Z14" s="80"/>
-      <c r="AA14" s="80"/>
-      <c r="AB14" s="80"/>
-      <c r="AC14" s="80"/>
-      <c r="AD14" s="80"/>
-      <c r="AE14" s="80"/>
-      <c r="AF14" s="80"/>
-      <c r="AG14" s="80"/>
-      <c r="AH14" s="80"/>
-      <c r="AI14" s="80"/>
-      <c r="AJ14" s="80"/>
-      <c r="AK14" s="80"/>
-      <c r="AL14" s="81"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="88"/>
+      <c r="AG14" s="88"/>
+      <c r="AH14" s="88"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="88"/>
+      <c r="AK14" s="88"/>
+      <c r="AL14" s="89"/>
     </row>
     <row r="15" spans="3:56" ht="11.25" customHeight="1">
-      <c r="C15" s="50"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="51"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
-      <c r="Z15" s="51"/>
-      <c r="AA15" s="51"/>
-      <c r="AB15" s="51"/>
-      <c r="AC15" s="51"/>
-      <c r="AD15" s="51"/>
-      <c r="AE15" s="51"/>
-      <c r="AF15" s="51"/>
-      <c r="AG15" s="51"/>
-      <c r="AH15" s="51"/>
-      <c r="AI15" s="51"/>
-      <c r="AJ15" s="51"/>
-      <c r="AK15" s="51"/>
-      <c r="AL15" s="53"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="48"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="51"/>
     </row>
     <row r="16" spans="3:56" ht="11.25" customHeight="1">
-      <c r="C16" s="39"/>
+      <c r="C16" s="37"/>
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
@@ -1811,7 +1857,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="21"/>
       <c r="T16" s="21"/>
-      <c r="U16" s="39"/>
+      <c r="U16" s="37"/>
       <c r="V16" s="21"/>
       <c r="W16" s="21"/>
       <c r="X16" s="21"/>
@@ -1831,7 +1877,7 @@
       <c r="AL16" s="22"/>
     </row>
     <row r="17" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C17" s="39"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="27" t="s">
         <v>7</v>
       </c>
@@ -1845,11 +1891,11 @@
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
+      <c r="O17" s="92"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="92"/>
+      <c r="S17" s="92"/>
       <c r="T17" s="21"/>
       <c r="U17" s="20"/>
       <c r="V17" s="21"/>
@@ -1871,19 +1917,19 @@
       <c r="AL17" s="22"/>
     </row>
     <row r="18" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C18" s="39"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="21" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="86" t="s">
+      <c r="G18" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
@@ -1909,19 +1955,19 @@
       <c r="AL18" s="22"/>
     </row>
     <row r="19" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C19" s="39"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="21" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="86" t="s">
+      <c r="G19" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="93"/>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
@@ -1947,19 +1993,19 @@
       <c r="AL19" s="22"/>
     </row>
     <row r="20" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C20" s="39"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="21" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="86" t="s">
+      <c r="G20" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="93"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
@@ -1985,19 +2031,19 @@
       <c r="AL20" s="22"/>
     </row>
     <row r="21" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C21" s="39"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="21" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="86" t="s">
+      <c r="G21" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
@@ -2023,19 +2069,19 @@
       <c r="AL21" s="22"/>
     </row>
     <row r="22" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C22" s="39"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="21" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="86" t="s">
+      <c r="G22" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
       <c r="N22" s="21"/>
@@ -2061,7 +2107,7 @@
       <c r="AL22" s="22"/>
     </row>
     <row r="23" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C23" s="39"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -2095,7 +2141,7 @@
       <c r="AL23" s="22"/>
     </row>
     <row r="24" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C24" s="39"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="27"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -2129,7 +2175,7 @@
       <c r="AL24" s="22"/>
     </row>
     <row r="25" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C25" s="39"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
       <c r="F25" s="5"/>
@@ -2163,12 +2209,12 @@
       <c r="AL25" s="22"/>
     </row>
     <row r="26" spans="3:38" ht="11.25" customHeight="1" thickBot="1">
-      <c r="C26" s="39"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
-      <c r="H26" s="40"/>
+      <c r="H26" s="38"/>
       <c r="I26" s="21"/>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
@@ -2187,7 +2233,7 @@
       <c r="X26" s="21"/>
       <c r="Y26" s="21"/>
       <c r="Z26" s="21"/>
-      <c r="AA26" s="41"/>
+      <c r="AA26" s="39"/>
       <c r="AB26" s="21"/>
       <c r="AC26" s="21"/>
       <c r="AD26" s="21"/>
@@ -2201,64 +2247,64 @@
       <c r="AL26" s="22"/>
     </row>
     <row r="27" spans="3:38" ht="16.5" thickBot="1">
-      <c r="C27" s="82" t="s">
+      <c r="C27" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="83"/>
-      <c r="T27" s="83"/>
-      <c r="U27" s="83"/>
-      <c r="V27" s="83"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="83"/>
-      <c r="Y27" s="83"/>
-      <c r="Z27" s="83"/>
-      <c r="AA27" s="83"/>
-      <c r="AB27" s="83"/>
-      <c r="AC27" s="83"/>
-      <c r="AD27" s="83"/>
-      <c r="AE27" s="83"/>
-      <c r="AF27" s="83"/>
-      <c r="AG27" s="83"/>
-      <c r="AH27" s="83"/>
-      <c r="AI27" s="83"/>
-      <c r="AJ27" s="83"/>
-      <c r="AK27" s="83"/>
-      <c r="AL27" s="84"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="103"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="103"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="103"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="103"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="90"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="90"/>
+      <c r="AE27" s="90"/>
+      <c r="AF27" s="90"/>
+      <c r="AG27" s="90"/>
+      <c r="AH27" s="90"/>
+      <c r="AI27" s="90"/>
+      <c r="AJ27" s="90"/>
+      <c r="AK27" s="90"/>
+      <c r="AL27" s="91"/>
     </row>
     <row r="28" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C28" s="39"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="105"/>
+      <c r="Q28" s="105"/>
+      <c r="R28" s="105"/>
+      <c r="S28" s="106"/>
+      <c r="T28" s="107"/>
       <c r="U28" s="27"/>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
@@ -2279,24 +2325,24 @@
       <c r="AL28" s="22"/>
     </row>
     <row r="29" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C29" s="39"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="2"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="110"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="110"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="111"/>
+      <c r="T29" s="42"/>
       <c r="U29" s="27"/>
       <c r="V29" s="21"/>
       <c r="W29" s="21"/>
@@ -2317,25 +2363,25 @@
       <c r="AL29" s="22"/>
     </row>
     <row r="30" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C30" s="39"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="52"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="110"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="50"/>
       <c r="V30" s="21"/>
       <c r="W30" s="21"/>
       <c r="X30" s="21"/>
@@ -2355,24 +2401,24 @@
       <c r="AL30" s="22"/>
     </row>
     <row r="31" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C31" s="39"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="109"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="109"/>
+      <c r="N31" s="109"/>
+      <c r="O31" s="109"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="109"/>
+      <c r="R31" s="109"/>
+      <c r="S31" s="109"/>
+      <c r="T31" s="42"/>
       <c r="U31" s="21"/>
       <c r="V31" s="21"/>
       <c r="W31" s="21"/>
@@ -2393,24 +2439,24 @@
       <c r="AL31" s="22"/>
     </row>
     <row r="32" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C32" s="39"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="21"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="115"/>
+      <c r="R32" s="115"/>
+      <c r="S32" s="109"/>
+      <c r="T32" s="22"/>
       <c r="U32" s="21"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
@@ -2428,27 +2474,27 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
       <c r="AK32" s="2"/>
-      <c r="AL32" s="44"/>
+      <c r="AL32" s="42"/>
     </row>
     <row r="33" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C33" s="39"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="109"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="109"/>
+      <c r="M33" s="109"/>
+      <c r="N33" s="109"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
+      <c r="S33" s="109"/>
+      <c r="T33" s="42"/>
       <c r="U33" s="21"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
@@ -2466,27 +2512,27 @@
       <c r="AI33" s="2"/>
       <c r="AJ33" s="2"/>
       <c r="AK33" s="2"/>
-      <c r="AL33" s="45"/>
+      <c r="AL33" s="43"/>
     </row>
     <row r="34" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C34" s="39"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="56"/>
-      <c r="N34" s="56"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="110"/>
+      <c r="M34" s="110"/>
+      <c r="N34" s="110"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="Q34" s="108"/>
+      <c r="R34" s="109"/>
+      <c r="S34" s="109"/>
+      <c r="T34" s="42"/>
       <c r="U34" s="21"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
@@ -2504,28 +2550,28 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
       <c r="AK34" s="2"/>
-      <c r="AL34" s="44"/>
+      <c r="AL34" s="42"/>
       <c r="AM34" s="4"/>
     </row>
     <row r="35" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C35" s="39"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="56"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="110"/>
+      <c r="M35" s="110"/>
+      <c r="N35" s="110"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="109"/>
+      <c r="S35" s="109"/>
+      <c r="T35" s="42"/>
       <c r="U35" s="21"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
@@ -2543,28 +2589,28 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
       <c r="AK35" s="2"/>
-      <c r="AL35" s="45"/>
+      <c r="AL35" s="43"/>
       <c r="AM35" s="4"/>
     </row>
     <row r="36" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C36" s="39"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="56"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="110"/>
+      <c r="G36" s="110"/>
+      <c r="H36" s="110"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="110"/>
+      <c r="N36" s="110"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="108"/>
+      <c r="Q36" s="108"/>
+      <c r="R36" s="109"/>
+      <c r="S36" s="109"/>
+      <c r="T36" s="42"/>
       <c r="U36" s="27"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
@@ -2582,28 +2628,28 @@
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
       <c r="AK36" s="2"/>
-      <c r="AL36" s="44"/>
+      <c r="AL36" s="42"/>
       <c r="AM36" s="4"/>
     </row>
     <row r="37" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C37" s="39"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="109"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="109"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="109"/>
+      <c r="N37" s="109"/>
+      <c r="O37" s="109"/>
+      <c r="P37" s="109"/>
+      <c r="Q37" s="109"/>
+      <c r="R37" s="109"/>
+      <c r="S37" s="109"/>
+      <c r="T37" s="42"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
@@ -2620,28 +2666,28 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
       <c r="AK37" s="2"/>
-      <c r="AL37" s="44"/>
+      <c r="AL37" s="42"/>
       <c r="AM37" s="4"/>
     </row>
     <row r="38" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C38" s="39"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="109"/>
+      <c r="N38" s="109"/>
+      <c r="O38" s="109"/>
+      <c r="P38" s="109"/>
+      <c r="Q38" s="109"/>
+      <c r="R38" s="109"/>
+      <c r="S38" s="109"/>
+      <c r="T38" s="42"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
@@ -2658,28 +2704,28 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
       <c r="AK38" s="2"/>
-      <c r="AL38" s="45"/>
+      <c r="AL38" s="43"/>
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C39" s="42"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="110"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="110"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="110"/>
+      <c r="M39" s="110"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="108"/>
+      <c r="P39" s="108"/>
+      <c r="Q39" s="108"/>
+      <c r="R39" s="117"/>
+      <c r="S39" s="117"/>
+      <c r="T39" s="43"/>
       <c r="V39" s="21"/>
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
@@ -2696,28 +2742,28 @@
       <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
-      <c r="AL39" s="44"/>
+      <c r="AL39" s="42"/>
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C40" s="39"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="109"/>
+      <c r="F40" s="110"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="110"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="110"/>
+      <c r="M40" s="110"/>
+      <c r="N40" s="110"/>
+      <c r="O40" s="108"/>
+      <c r="P40" s="108"/>
+      <c r="Q40" s="108"/>
+      <c r="R40" s="109"/>
+      <c r="S40" s="109"/>
+      <c r="T40" s="42"/>
       <c r="V40" s="21"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
@@ -2734,29 +2780,29 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
       <c r="AK40" s="2"/>
-      <c r="AL40" s="44"/>
+      <c r="AL40" s="42"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="35"/>
+      <c r="AN40" s="33"/>
     </row>
     <row r="41" spans="3:47" ht="11.1" customHeight="1">
-      <c r="C41" s="39"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="21"/>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="109"/>
+      <c r="F41" s="110"/>
+      <c r="G41" s="110"/>
+      <c r="H41" s="110"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="110"/>
+      <c r="M41" s="110"/>
+      <c r="N41" s="110"/>
+      <c r="O41" s="108"/>
+      <c r="P41" s="108"/>
+      <c r="Q41" s="108"/>
+      <c r="R41" s="109"/>
+      <c r="S41" s="109"/>
+      <c r="T41" s="42"/>
       <c r="V41" s="21"/>
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
@@ -2773,29 +2819,29 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
       <c r="AK41" s="2"/>
-      <c r="AL41" s="45"/>
+      <c r="AL41" s="43"/>
       <c r="AM41" s="4"/>
       <c r="AN41" s="6"/>
     </row>
     <row r="42" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C42" s="39"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="109"/>
+      <c r="F42" s="109"/>
+      <c r="G42" s="109"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="109"/>
+      <c r="J42" s="109"/>
+      <c r="K42" s="109"/>
+      <c r="L42" s="109"/>
+      <c r="M42" s="109"/>
+      <c r="N42" s="109"/>
+      <c r="O42" s="109"/>
+      <c r="P42" s="109"/>
+      <c r="Q42" s="109"/>
+      <c r="R42" s="109"/>
+      <c r="S42" s="109"/>
+      <c r="T42" s="42"/>
       <c r="V42" s="21"/>
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
@@ -2812,29 +2858,29 @@
       <c r="AI42" s="2"/>
       <c r="AJ42" s="2"/>
       <c r="AK42" s="2"/>
-      <c r="AL42" s="44"/>
+      <c r="AL42" s="42"/>
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
     </row>
     <row r="43" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C43" s="39"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="2"/>
-      <c r="T43" s="2"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="109"/>
+      <c r="E43" s="109"/>
+      <c r="F43" s="109"/>
+      <c r="G43" s="109"/>
+      <c r="H43" s="109"/>
+      <c r="I43" s="109"/>
+      <c r="J43" s="109"/>
+      <c r="K43" s="109"/>
+      <c r="L43" s="109"/>
+      <c r="M43" s="109"/>
+      <c r="N43" s="109"/>
+      <c r="O43" s="109"/>
+      <c r="P43" s="109"/>
+      <c r="Q43" s="109"/>
+      <c r="R43" s="109"/>
+      <c r="S43" s="109"/>
+      <c r="T43" s="42"/>
       <c r="V43" s="21"/>
       <c r="W43" s="2"/>
       <c r="AA43" s="2"/>
@@ -2848,10 +2894,10 @@
       <c r="AI43" s="2"/>
       <c r="AJ43" s="2"/>
       <c r="AK43" s="2"/>
-      <c r="AL43" s="44"/>
+      <c r="AL43" s="42"/>
       <c r="AM43" s="4"/>
       <c r="AN43" s="28"/>
-      <c r="AP43" s="52"/>
+      <c r="AP43" s="50"/>
       <c r="AQ43" s="21"/>
       <c r="AR43" s="2"/>
       <c r="AS43" s="2"/>
@@ -2859,24 +2905,24 @@
       <c r="AU43" s="2"/>
     </row>
     <row r="44" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C44" s="39"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="2"/>
-      <c r="T44" s="2"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="109"/>
+      <c r="E44" s="109"/>
+      <c r="F44" s="109"/>
+      <c r="G44" s="109"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="109"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="109"/>
+      <c r="L44" s="109"/>
+      <c r="M44" s="109"/>
+      <c r="N44" s="109"/>
+      <c r="O44" s="109"/>
+      <c r="P44" s="109"/>
+      <c r="Q44" s="109"/>
+      <c r="R44" s="109"/>
+      <c r="S44" s="109"/>
+      <c r="T44" s="42"/>
       <c r="V44" s="21"/>
       <c r="W44" s="2"/>
       <c r="AA44" s="2"/>
@@ -2890,10 +2936,10 @@
       <c r="AI44" s="2"/>
       <c r="AJ44" s="2"/>
       <c r="AK44" s="2"/>
-      <c r="AL44" s="44"/>
+      <c r="AL44" s="42"/>
       <c r="AM44" s="4"/>
       <c r="AN44" s="6"/>
-      <c r="AP44" s="52"/>
+      <c r="AP44" s="50"/>
       <c r="AQ44" s="21"/>
       <c r="AR44" s="2"/>
       <c r="AS44" s="2"/>
@@ -2901,24 +2947,24 @@
       <c r="AU44" s="2"/>
     </row>
     <row r="45" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C45" s="39"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="119"/>
+      <c r="N45" s="119"/>
+      <c r="O45" s="119"/>
+      <c r="P45" s="119"/>
+      <c r="Q45" s="119"/>
+      <c r="R45" s="119"/>
+      <c r="S45" s="119"/>
+      <c r="T45" s="120"/>
       <c r="V45" s="21"/>
       <c r="W45" s="2"/>
       <c r="AA45" s="2"/>
@@ -2932,8 +2978,8 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
       <c r="AK45" s="2"/>
-      <c r="AL45" s="45"/>
-      <c r="AP45" s="52"/>
+      <c r="AL45" s="43"/>
+      <c r="AP45" s="50"/>
       <c r="AQ45" s="21"/>
       <c r="AR45" s="2"/>
       <c r="AS45" s="2"/>
@@ -2941,48 +2987,48 @@
       <c r="AU45" s="2"/>
     </row>
     <row r="46" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C46" s="38"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="43"/>
-      <c r="M46" s="43"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="43"/>
-      <c r="P46" s="43"/>
-      <c r="Q46" s="43"/>
-      <c r="R46" s="43"/>
-      <c r="S46" s="43"/>
-      <c r="T46" s="43"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="41"/>
       <c r="U46" s="17"/>
       <c r="V46" s="14"/>
-      <c r="W46" s="43"/>
+      <c r="W46" s="41"/>
       <c r="X46" s="17"/>
       <c r="Y46" s="17"/>
       <c r="Z46" s="17"/>
-      <c r="AA46" s="43"/>
-      <c r="AB46" s="43"/>
-      <c r="AC46" s="43"/>
-      <c r="AD46" s="43"/>
-      <c r="AE46" s="43"/>
-      <c r="AF46" s="43"/>
-      <c r="AG46" s="43"/>
-      <c r="AH46" s="43"/>
-      <c r="AI46" s="43"/>
-      <c r="AJ46" s="43"/>
-      <c r="AK46" s="43"/>
-      <c r="AL46" s="57"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="41"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="41"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="41"/>
+      <c r="AK46" s="41"/>
+      <c r="AL46" s="52"/>
     </row>
     <row r="47" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="59" t="s">
+      <c r="D47" s="54" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="2"/>
@@ -3017,748 +3063,748 @@
       <c r="AI47" s="2"/>
       <c r="AJ47" s="2"/>
       <c r="AK47" s="2"/>
-      <c r="AL47" s="44"/>
+      <c r="AL47" s="42"/>
     </row>
     <row r="48" spans="3:47" ht="11.25" customHeight="1">
-      <c r="C48" s="34"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="46"/>
-      <c r="T48" s="46"/>
-      <c r="U48" s="46"/>
-      <c r="V48" s="46"/>
-      <c r="W48" s="46"/>
-      <c r="X48" s="46"/>
-      <c r="Y48" s="46"/>
-      <c r="Z48" s="46"/>
-      <c r="AA48" s="46"/>
-      <c r="AB48" s="46"/>
-      <c r="AC48" s="46"/>
-      <c r="AD48" s="46"/>
-      <c r="AE48" s="46"/>
-      <c r="AF48" s="46"/>
-      <c r="AG48" s="46"/>
-      <c r="AH48" s="46"/>
-      <c r="AI48" s="46"/>
-      <c r="AJ48" s="46"/>
-      <c r="AK48" s="46"/>
-      <c r="AL48" s="47"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="44"/>
+      <c r="S48" s="44"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="44"/>
+      <c r="V48" s="44"/>
+      <c r="W48" s="44"/>
+      <c r="X48" s="44"/>
+      <c r="Y48" s="44"/>
+      <c r="Z48" s="44"/>
+      <c r="AA48" s="44"/>
+      <c r="AB48" s="44"/>
+      <c r="AC48" s="44"/>
+      <c r="AD48" s="44"/>
+      <c r="AE48" s="44"/>
+      <c r="AF48" s="44"/>
+      <c r="AG48" s="44"/>
+      <c r="AH48" s="44"/>
+      <c r="AI48" s="44"/>
+      <c r="AJ48" s="44"/>
+      <c r="AK48" s="44"/>
+      <c r="AL48" s="45"/>
     </row>
     <row r="49" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C49" s="34" t="s">
+      <c r="C49" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="46"/>
-      <c r="Q49" s="46"/>
-      <c r="R49" s="46"/>
-      <c r="S49" s="46"/>
-      <c r="T49" s="46"/>
-      <c r="U49" s="46"/>
-      <c r="V49" s="46"/>
-      <c r="W49" s="46"/>
-      <c r="X49" s="46"/>
-      <c r="Y49" s="46"/>
-      <c r="Z49" s="46"/>
-      <c r="AA49" s="46"/>
-      <c r="AB49" s="46"/>
-      <c r="AC49" s="46"/>
-      <c r="AD49" s="46"/>
-      <c r="AE49" s="46"/>
-      <c r="AF49" s="46"/>
-      <c r="AG49" s="46"/>
-      <c r="AH49" s="46"/>
-      <c r="AI49" s="46"/>
-      <c r="AJ49" s="46"/>
-      <c r="AK49" s="46"/>
-      <c r="AL49" s="47"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="44"/>
+      <c r="R49" s="44"/>
+      <c r="S49" s="44"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="44"/>
+      <c r="V49" s="44"/>
+      <c r="W49" s="44"/>
+      <c r="X49" s="44"/>
+      <c r="Y49" s="44"/>
+      <c r="Z49" s="44"/>
+      <c r="AA49" s="44"/>
+      <c r="AB49" s="44"/>
+      <c r="AC49" s="44"/>
+      <c r="AD49" s="44"/>
+      <c r="AE49" s="44"/>
+      <c r="AF49" s="44"/>
+      <c r="AG49" s="44"/>
+      <c r="AH49" s="44"/>
+      <c r="AI49" s="44"/>
+      <c r="AJ49" s="44"/>
+      <c r="AK49" s="44"/>
+      <c r="AL49" s="45"/>
     </row>
     <row r="50" spans="3:38" ht="11.1" customHeight="1">
-      <c r="C50" s="34" t="s">
+      <c r="C50" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
-      <c r="V50" s="46"/>
-      <c r="W50" s="46"/>
-      <c r="X50" s="46"/>
-      <c r="Y50" s="46"/>
-      <c r="Z50" s="46"/>
-      <c r="AA50" s="46"/>
-      <c r="AB50" s="46"/>
-      <c r="AC50" s="46"/>
-      <c r="AD50" s="46"/>
-      <c r="AE50" s="46"/>
-      <c r="AF50" s="46"/>
-      <c r="AG50" s="46"/>
-      <c r="AH50" s="46"/>
-      <c r="AI50" s="46"/>
-      <c r="AJ50" s="46"/>
-      <c r="AK50" s="46"/>
-      <c r="AL50" s="47"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="44"/>
+      <c r="AA50" s="44"/>
+      <c r="AB50" s="44"/>
+      <c r="AC50" s="44"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
+      <c r="AH50" s="44"/>
+      <c r="AI50" s="44"/>
+      <c r="AJ50" s="44"/>
+      <c r="AK50" s="44"/>
+      <c r="AL50" s="45"/>
     </row>
     <row r="51" spans="3:38" ht="11.1" customHeight="1">
-      <c r="C51" s="34" t="s">
+      <c r="C51" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="46"/>
-      <c r="U51" s="46"/>
-      <c r="V51" s="46"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="46"/>
-      <c r="Y51" s="46"/>
-      <c r="Z51" s="46"/>
-      <c r="AA51" s="46"/>
-      <c r="AB51" s="46"/>
-      <c r="AC51" s="46"/>
-      <c r="AD51" s="46"/>
-      <c r="AE51" s="46"/>
-      <c r="AF51" s="46"/>
-      <c r="AG51" s="46"/>
-      <c r="AH51" s="46"/>
-      <c r="AI51" s="46"/>
-      <c r="AJ51" s="46"/>
-      <c r="AK51" s="46"/>
-      <c r="AL51" s="47"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="44"/>
+      <c r="T51" s="44"/>
+      <c r="U51" s="44"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="44"/>
+      <c r="X51" s="44"/>
+      <c r="Y51" s="44"/>
+      <c r="Z51" s="44"/>
+      <c r="AA51" s="44"/>
+      <c r="AB51" s="44"/>
+      <c r="AC51" s="44"/>
+      <c r="AD51" s="44"/>
+      <c r="AE51" s="44"/>
+      <c r="AF51" s="44"/>
+      <c r="AG51" s="44"/>
+      <c r="AH51" s="44"/>
+      <c r="AI51" s="44"/>
+      <c r="AJ51" s="44"/>
+      <c r="AK51" s="44"/>
+      <c r="AL51" s="45"/>
     </row>
     <row r="52" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C52" s="34" t="s">
+      <c r="C52" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="46"/>
-      <c r="S52" s="46"/>
-      <c r="T52" s="46"/>
-      <c r="U52" s="46"/>
-      <c r="V52" s="46"/>
-      <c r="W52" s="46"/>
-      <c r="X52" s="46"/>
-      <c r="Y52" s="46"/>
-      <c r="Z52" s="46"/>
-      <c r="AA52" s="46"/>
-      <c r="AB52" s="46" t="s">
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+      <c r="P52" s="44"/>
+      <c r="Q52" s="44"/>
+      <c r="R52" s="44"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="44"/>
+      <c r="V52" s="44"/>
+      <c r="W52" s="44"/>
+      <c r="X52" s="44"/>
+      <c r="Y52" s="44"/>
+      <c r="Z52" s="44"/>
+      <c r="AA52" s="44"/>
+      <c r="AB52" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AC52" s="46"/>
-      <c r="AD52" s="46"/>
-      <c r="AE52" s="46"/>
-      <c r="AF52" s="46"/>
-      <c r="AG52" s="46"/>
-      <c r="AH52" s="46"/>
-      <c r="AI52" s="46"/>
-      <c r="AJ52" s="46"/>
-      <c r="AK52" s="46"/>
-      <c r="AL52" s="47"/>
+      <c r="AC52" s="44"/>
+      <c r="AD52" s="44"/>
+      <c r="AE52" s="44"/>
+      <c r="AF52" s="44"/>
+      <c r="AG52" s="44"/>
+      <c r="AH52" s="44"/>
+      <c r="AI52" s="44"/>
+      <c r="AJ52" s="44"/>
+      <c r="AK52" s="44"/>
+      <c r="AL52" s="45"/>
     </row>
     <row r="53" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46"/>
-      <c r="R53" s="46"/>
-      <c r="S53" s="46"/>
-      <c r="T53" s="46"/>
-      <c r="U53" s="46"/>
-      <c r="V53" s="46"/>
-      <c r="W53" s="46"/>
-      <c r="X53" s="46"/>
-      <c r="Y53" s="46"/>
-      <c r="Z53" s="46"/>
-      <c r="AA53" s="46"/>
-      <c r="AB53" s="46"/>
-      <c r="AC53" s="46"/>
-      <c r="AD53" s="46"/>
-      <c r="AE53" s="46"/>
-      <c r="AF53" s="46"/>
-      <c r="AG53" s="46"/>
-      <c r="AH53" s="46"/>
-      <c r="AI53" s="46"/>
-      <c r="AJ53" s="46"/>
-      <c r="AK53" s="46"/>
-      <c r="AL53" s="47"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="44"/>
+      <c r="M53" s="44"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+      <c r="P53" s="44"/>
+      <c r="Q53" s="44"/>
+      <c r="R53" s="44"/>
+      <c r="S53" s="44"/>
+      <c r="T53" s="44"/>
+      <c r="U53" s="44"/>
+      <c r="V53" s="44"/>
+      <c r="W53" s="44"/>
+      <c r="X53" s="44"/>
+      <c r="Y53" s="44"/>
+      <c r="Z53" s="44"/>
+      <c r="AA53" s="44"/>
+      <c r="AB53" s="44"/>
+      <c r="AC53" s="44"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="44"/>
+      <c r="AF53" s="44"/>
+      <c r="AG53" s="44"/>
+      <c r="AH53" s="44"/>
+      <c r="AI53" s="44"/>
+      <c r="AJ53" s="44"/>
+      <c r="AK53" s="44"/>
+      <c r="AL53" s="45"/>
     </row>
     <row r="54" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C54" s="34" t="s">
+      <c r="C54" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="46"/>
-      <c r="R54" s="46"/>
-      <c r="S54" s="46"/>
-      <c r="T54" s="46"/>
-      <c r="U54" s="46"/>
-      <c r="V54" s="46"/>
-      <c r="W54" s="46"/>
-      <c r="X54" s="46"/>
-      <c r="Y54" s="46"/>
-      <c r="Z54" s="46"/>
-      <c r="AA54" s="46"/>
-      <c r="AB54" s="46"/>
-      <c r="AC54" s="46"/>
-      <c r="AD54" s="46"/>
-      <c r="AE54" s="46"/>
-      <c r="AF54" s="46"/>
-      <c r="AG54" s="46"/>
-      <c r="AH54" s="46"/>
-      <c r="AI54" s="46"/>
-      <c r="AJ54" s="46"/>
-      <c r="AK54" s="46"/>
-      <c r="AL54" s="47"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="44"/>
+      <c r="N54" s="44"/>
+      <c r="O54" s="44"/>
+      <c r="P54" s="44"/>
+      <c r="Q54" s="44"/>
+      <c r="R54" s="44"/>
+      <c r="S54" s="44"/>
+      <c r="T54" s="44"/>
+      <c r="U54" s="44"/>
+      <c r="V54" s="44"/>
+      <c r="W54" s="44"/>
+      <c r="X54" s="44"/>
+      <c r="Y54" s="44"/>
+      <c r="Z54" s="44"/>
+      <c r="AA54" s="44"/>
+      <c r="AB54" s="44"/>
+      <c r="AC54" s="44"/>
+      <c r="AD54" s="44"/>
+      <c r="AE54" s="44"/>
+      <c r="AF54" s="44"/>
+      <c r="AG54" s="44"/>
+      <c r="AH54" s="44"/>
+      <c r="AI54" s="44"/>
+      <c r="AJ54" s="44"/>
+      <c r="AK54" s="44"/>
+      <c r="AL54" s="45"/>
     </row>
     <row r="55" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C55" s="34" t="s">
+      <c r="C55" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="46"/>
-      <c r="R55" s="46"/>
-      <c r="S55" s="46"/>
-      <c r="T55" s="46"/>
-      <c r="U55" s="46"/>
-      <c r="V55" s="46"/>
-      <c r="W55" s="46"/>
-      <c r="X55" s="46"/>
-      <c r="Y55" s="46"/>
-      <c r="Z55" s="46"/>
-      <c r="AA55" s="46"/>
-      <c r="AB55" s="46"/>
-      <c r="AC55" s="46"/>
-      <c r="AD55" s="46"/>
-      <c r="AE55" s="46"/>
-      <c r="AF55" s="46"/>
-      <c r="AG55" s="46"/>
-      <c r="AH55" s="46"/>
-      <c r="AI55" s="46"/>
-      <c r="AJ55" s="46"/>
-      <c r="AK55" s="46"/>
-      <c r="AL55" s="47"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="44"/>
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
+      <c r="P55" s="44"/>
+      <c r="Q55" s="44"/>
+      <c r="R55" s="44"/>
+      <c r="S55" s="44"/>
+      <c r="T55" s="44"/>
+      <c r="U55" s="44"/>
+      <c r="V55" s="44"/>
+      <c r="W55" s="44"/>
+      <c r="X55" s="44"/>
+      <c r="Y55" s="44"/>
+      <c r="Z55" s="44"/>
+      <c r="AA55" s="44"/>
+      <c r="AB55" s="44"/>
+      <c r="AC55" s="44"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="44"/>
+      <c r="AF55" s="44"/>
+      <c r="AG55" s="44"/>
+      <c r="AH55" s="44"/>
+      <c r="AI55" s="44"/>
+      <c r="AJ55" s="44"/>
+      <c r="AK55" s="44"/>
+      <c r="AL55" s="45"/>
     </row>
     <row r="56" spans="3:38" ht="11.25" customHeight="1">
       <c r="C56" s="10"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46"/>
-      <c r="R56" s="46"/>
-      <c r="S56" s="46"/>
-      <c r="T56" s="46"/>
-      <c r="U56" s="46"/>
-      <c r="V56" s="46"/>
-      <c r="W56" s="46"/>
-      <c r="X56" s="46"/>
-      <c r="Y56" s="46"/>
-      <c r="Z56" s="46"/>
-      <c r="AA56" s="46"/>
-      <c r="AB56" s="46"/>
-      <c r="AC56" s="46"/>
-      <c r="AD56" s="46"/>
-      <c r="AE56" s="46"/>
-      <c r="AF56" s="46"/>
-      <c r="AG56" s="46"/>
-      <c r="AH56" s="46"/>
-      <c r="AI56" s="46"/>
-      <c r="AJ56" s="46"/>
-      <c r="AK56" s="46"/>
-      <c r="AL56" s="47"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="44"/>
+      <c r="S56" s="44"/>
+      <c r="T56" s="44"/>
+      <c r="U56" s="44"/>
+      <c r="V56" s="44"/>
+      <c r="W56" s="44"/>
+      <c r="X56" s="44"/>
+      <c r="Y56" s="44"/>
+      <c r="Z56" s="44"/>
+      <c r="AA56" s="44"/>
+      <c r="AB56" s="44"/>
+      <c r="AC56" s="44"/>
+      <c r="AD56" s="44"/>
+      <c r="AE56" s="44"/>
+      <c r="AF56" s="44"/>
+      <c r="AG56" s="44"/>
+      <c r="AH56" s="44"/>
+      <c r="AI56" s="44"/>
+      <c r="AJ56" s="44"/>
+      <c r="AK56" s="44"/>
+      <c r="AL56" s="45"/>
     </row>
     <row r="57" spans="3:38" ht="11.25" customHeight="1">
       <c r="C57" s="10"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="46"/>
-      <c r="R57" s="46"/>
-      <c r="S57" s="46"/>
-      <c r="T57" s="46"/>
-      <c r="U57" s="46"/>
-      <c r="V57" s="46"/>
-      <c r="W57" s="46"/>
-      <c r="X57" s="46"/>
-      <c r="Y57" s="46"/>
-      <c r="Z57" s="46"/>
-      <c r="AA57" s="46"/>
-      <c r="AB57" s="46"/>
-      <c r="AC57" s="46"/>
-      <c r="AD57" s="46"/>
-      <c r="AE57" s="46"/>
-      <c r="AF57" s="46"/>
-      <c r="AG57" s="46"/>
-      <c r="AH57" s="46"/>
-      <c r="AI57" s="46"/>
-      <c r="AJ57" s="46"/>
-      <c r="AK57" s="46"/>
-      <c r="AL57" s="47"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
+      <c r="M57" s="44"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="44"/>
+      <c r="P57" s="44"/>
+      <c r="Q57" s="44"/>
+      <c r="R57" s="44"/>
+      <c r="S57" s="44"/>
+      <c r="T57" s="44"/>
+      <c r="U57" s="44"/>
+      <c r="V57" s="44"/>
+      <c r="W57" s="44"/>
+      <c r="X57" s="44"/>
+      <c r="Y57" s="44"/>
+      <c r="Z57" s="44"/>
+      <c r="AA57" s="44"/>
+      <c r="AB57" s="44"/>
+      <c r="AC57" s="44"/>
+      <c r="AD57" s="44"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="44"/>
+      <c r="AJ57" s="44"/>
+      <c r="AK57" s="44"/>
+      <c r="AL57" s="45"/>
     </row>
     <row r="58" spans="3:38" ht="11.25" customHeight="1">
       <c r="C58" s="10"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
-      <c r="M58" s="46"/>
-      <c r="N58" s="46"/>
-      <c r="O58" s="46"/>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="46"/>
-      <c r="S58" s="46"/>
-      <c r="T58" s="46"/>
-      <c r="U58" s="46"/>
-      <c r="V58" s="46"/>
-      <c r="W58" s="46"/>
-      <c r="X58" s="46"/>
-      <c r="Y58" s="46"/>
-      <c r="Z58" s="46"/>
-      <c r="AA58" s="46"/>
-      <c r="AB58" s="46"/>
-      <c r="AC58" s="46"/>
-      <c r="AD58" s="46"/>
-      <c r="AE58" s="46"/>
-      <c r="AF58" s="46"/>
-      <c r="AG58" s="46"/>
-      <c r="AH58" s="46"/>
-      <c r="AI58" s="46"/>
-      <c r="AJ58" s="46"/>
-      <c r="AK58" s="46"/>
-      <c r="AL58" s="47"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
+      <c r="M58" s="44"/>
+      <c r="N58" s="44"/>
+      <c r="O58" s="44"/>
+      <c r="P58" s="44"/>
+      <c r="Q58" s="44"/>
+      <c r="R58" s="44"/>
+      <c r="S58" s="44"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="44"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="44"/>
+      <c r="X58" s="44"/>
+      <c r="Y58" s="44"/>
+      <c r="Z58" s="44"/>
+      <c r="AA58" s="44"/>
+      <c r="AB58" s="44"/>
+      <c r="AC58" s="44"/>
+      <c r="AD58" s="44"/>
+      <c r="AE58" s="44"/>
+      <c r="AF58" s="44"/>
+      <c r="AG58" s="44"/>
+      <c r="AH58" s="44"/>
+      <c r="AI58" s="44"/>
+      <c r="AJ58" s="44"/>
+      <c r="AK58" s="44"/>
+      <c r="AL58" s="45"/>
     </row>
     <row r="59" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C59" s="34"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
-      <c r="M59" s="46"/>
-      <c r="N59" s="46"/>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="46"/>
-      <c r="R59" s="46"/>
-      <c r="S59" s="46"/>
-      <c r="T59" s="46"/>
-      <c r="U59" s="46"/>
-      <c r="V59" s="46"/>
-      <c r="W59" s="46"/>
-      <c r="X59" s="46"/>
-      <c r="Y59" s="46"/>
-      <c r="Z59" s="46"/>
-      <c r="AA59" s="46"/>
-      <c r="AB59" s="46"/>
-      <c r="AC59" s="46"/>
-      <c r="AD59" s="46"/>
-      <c r="AE59" s="46"/>
-      <c r="AF59" s="46"/>
-      <c r="AG59" s="46"/>
-      <c r="AH59" s="46"/>
-      <c r="AI59" s="46"/>
-      <c r="AJ59" s="46"/>
-      <c r="AK59" s="46"/>
-      <c r="AL59" s="47"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="44"/>
+      <c r="M59" s="44"/>
+      <c r="N59" s="44"/>
+      <c r="O59" s="44"/>
+      <c r="P59" s="44"/>
+      <c r="Q59" s="44"/>
+      <c r="R59" s="44"/>
+      <c r="S59" s="44"/>
+      <c r="T59" s="44"/>
+      <c r="U59" s="44"/>
+      <c r="V59" s="44"/>
+      <c r="W59" s="44"/>
+      <c r="X59" s="44"/>
+      <c r="Y59" s="44"/>
+      <c r="Z59" s="44"/>
+      <c r="AA59" s="44"/>
+      <c r="AB59" s="44"/>
+      <c r="AC59" s="44"/>
+      <c r="AD59" s="44"/>
+      <c r="AE59" s="44"/>
+      <c r="AF59" s="44"/>
+      <c r="AG59" s="44"/>
+      <c r="AH59" s="44"/>
+      <c r="AI59" s="44"/>
+      <c r="AJ59" s="44"/>
+      <c r="AK59" s="44"/>
+      <c r="AL59" s="45"/>
     </row>
     <row r="60" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C60" s="34" t="s">
+      <c r="C60" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="58" t="s">
+      <c r="D60" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="46"/>
-      <c r="R60" s="46"/>
-      <c r="S60" s="46"/>
-      <c r="T60" s="46"/>
-      <c r="U60" s="46"/>
-      <c r="V60" s="46"/>
-      <c r="W60" s="46"/>
-      <c r="X60" s="46"/>
-      <c r="Y60" s="46"/>
-      <c r="Z60" s="46"/>
-      <c r="AA60" s="46"/>
-      <c r="AB60" s="46"/>
-      <c r="AC60" s="46"/>
-      <c r="AD60" s="46"/>
-      <c r="AE60" s="46"/>
-      <c r="AF60" s="46"/>
-      <c r="AG60" s="46"/>
-      <c r="AH60" s="46"/>
-      <c r="AI60" s="46"/>
-      <c r="AJ60" s="46"/>
-      <c r="AK60" s="46"/>
-      <c r="AL60" s="47"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+      <c r="L60" s="44"/>
+      <c r="M60" s="44"/>
+      <c r="N60" s="44"/>
+      <c r="O60" s="44"/>
+      <c r="P60" s="44"/>
+      <c r="Q60" s="44"/>
+      <c r="R60" s="44"/>
+      <c r="S60" s="44"/>
+      <c r="T60" s="44"/>
+      <c r="U60" s="44"/>
+      <c r="V60" s="44"/>
+      <c r="W60" s="44"/>
+      <c r="X60" s="44"/>
+      <c r="Y60" s="44"/>
+      <c r="Z60" s="44"/>
+      <c r="AA60" s="44"/>
+      <c r="AB60" s="44"/>
+      <c r="AC60" s="44"/>
+      <c r="AD60" s="44"/>
+      <c r="AE60" s="44"/>
+      <c r="AF60" s="44"/>
+      <c r="AG60" s="44"/>
+      <c r="AH60" s="44"/>
+      <c r="AI60" s="44"/>
+      <c r="AJ60" s="44"/>
+      <c r="AK60" s="44"/>
+      <c r="AL60" s="45"/>
     </row>
     <row r="61" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C61" s="34"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
-      <c r="M61" s="46"/>
-      <c r="N61" s="46"/>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="46"/>
-      <c r="R61" s="46"/>
-      <c r="S61" s="46"/>
-      <c r="T61" s="46"/>
-      <c r="U61" s="46"/>
-      <c r="V61" s="46"/>
-      <c r="W61" s="46"/>
-      <c r="X61" s="46"/>
-      <c r="Y61" s="46"/>
-      <c r="Z61" s="46"/>
-      <c r="AA61" s="46"/>
-      <c r="AB61" s="46"/>
-      <c r="AC61" s="46"/>
-      <c r="AD61" s="46"/>
-      <c r="AE61" s="46"/>
-      <c r="AF61" s="46"/>
-      <c r="AG61" s="46"/>
-      <c r="AH61" s="46"/>
-      <c r="AI61" s="46"/>
-      <c r="AJ61" s="46"/>
-      <c r="AK61" s="46"/>
-      <c r="AL61" s="47"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+      <c r="L61" s="44"/>
+      <c r="M61" s="44"/>
+      <c r="N61" s="44"/>
+      <c r="O61" s="44"/>
+      <c r="P61" s="44"/>
+      <c r="Q61" s="44"/>
+      <c r="R61" s="44"/>
+      <c r="S61" s="44"/>
+      <c r="T61" s="44"/>
+      <c r="U61" s="44"/>
+      <c r="V61" s="44"/>
+      <c r="W61" s="44"/>
+      <c r="X61" s="44"/>
+      <c r="Y61" s="44"/>
+      <c r="Z61" s="44"/>
+      <c r="AA61" s="44"/>
+      <c r="AB61" s="44"/>
+      <c r="AC61" s="44"/>
+      <c r="AD61" s="44"/>
+      <c r="AE61" s="44"/>
+      <c r="AF61" s="44"/>
+      <c r="AG61" s="44"/>
+      <c r="AH61" s="44"/>
+      <c r="AI61" s="44"/>
+      <c r="AJ61" s="44"/>
+      <c r="AK61" s="44"/>
+      <c r="AL61" s="45"/>
     </row>
     <row r="62" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="46"/>
-      <c r="M62" s="46"/>
-      <c r="N62" s="46"/>
-      <c r="O62" s="46"/>
-      <c r="P62" s="46"/>
-      <c r="Q62" s="46"/>
-      <c r="R62" s="46"/>
-      <c r="S62" s="46"/>
-      <c r="T62" s="46"/>
-      <c r="U62" s="46"/>
-      <c r="V62" s="46"/>
-      <c r="W62" s="46"/>
-      <c r="X62" s="46"/>
-      <c r="Y62" s="46"/>
-      <c r="Z62" s="46"/>
-      <c r="AA62" s="46"/>
-      <c r="AB62" s="46"/>
-      <c r="AC62" s="46"/>
-      <c r="AD62" s="46"/>
-      <c r="AE62" s="46"/>
-      <c r="AF62" s="46"/>
-      <c r="AG62" s="46"/>
-      <c r="AH62" s="46"/>
-      <c r="AI62" s="46"/>
-      <c r="AJ62" s="46"/>
-      <c r="AK62" s="46"/>
-      <c r="AL62" s="47"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="44"/>
+      <c r="L62" s="44"/>
+      <c r="M62" s="44"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="44"/>
+      <c r="P62" s="44"/>
+      <c r="Q62" s="44"/>
+      <c r="R62" s="44"/>
+      <c r="S62" s="44"/>
+      <c r="T62" s="44"/>
+      <c r="U62" s="44"/>
+      <c r="V62" s="44"/>
+      <c r="W62" s="44"/>
+      <c r="X62" s="44"/>
+      <c r="Y62" s="44"/>
+      <c r="Z62" s="44"/>
+      <c r="AA62" s="44"/>
+      <c r="AB62" s="44"/>
+      <c r="AC62" s="44"/>
+      <c r="AD62" s="44"/>
+      <c r="AE62" s="44"/>
+      <c r="AF62" s="44"/>
+      <c r="AG62" s="44"/>
+      <c r="AH62" s="44"/>
+      <c r="AI62" s="44"/>
+      <c r="AJ62" s="44"/>
+      <c r="AK62" s="44"/>
+      <c r="AL62" s="45"/>
     </row>
     <row r="63" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C63" s="34" t="s">
+      <c r="C63" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="46"/>
-      <c r="N63" s="46"/>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46"/>
-      <c r="Q63" s="46"/>
-      <c r="R63" s="46"/>
-      <c r="S63" s="46"/>
-      <c r="T63" s="46"/>
-      <c r="U63" s="46"/>
-      <c r="V63" s="46"/>
-      <c r="W63" s="46"/>
-      <c r="X63" s="46"/>
-      <c r="Y63" s="46"/>
-      <c r="Z63" s="46"/>
-      <c r="AA63" s="46"/>
-      <c r="AB63" s="46"/>
-      <c r="AC63" s="46"/>
-      <c r="AD63" s="46"/>
-      <c r="AE63" s="46"/>
-      <c r="AF63" s="46"/>
-      <c r="AG63" s="46"/>
-      <c r="AH63" s="46"/>
-      <c r="AI63" s="46"/>
-      <c r="AJ63" s="46"/>
-      <c r="AK63" s="46"/>
-      <c r="AL63" s="47"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="44"/>
+      <c r="K63" s="44"/>
+      <c r="L63" s="44"/>
+      <c r="M63" s="44"/>
+      <c r="N63" s="44"/>
+      <c r="O63" s="44"/>
+      <c r="P63" s="44"/>
+      <c r="Q63" s="44"/>
+      <c r="R63" s="44"/>
+      <c r="S63" s="44"/>
+      <c r="T63" s="44"/>
+      <c r="U63" s="44"/>
+      <c r="V63" s="44"/>
+      <c r="W63" s="44"/>
+      <c r="X63" s="44"/>
+      <c r="Y63" s="44"/>
+      <c r="Z63" s="44"/>
+      <c r="AA63" s="44"/>
+      <c r="AB63" s="44"/>
+      <c r="AC63" s="44"/>
+      <c r="AD63" s="44"/>
+      <c r="AE63" s="44"/>
+      <c r="AF63" s="44"/>
+      <c r="AG63" s="44"/>
+      <c r="AH63" s="44"/>
+      <c r="AI63" s="44"/>
+      <c r="AJ63" s="44"/>
+      <c r="AK63" s="44"/>
+      <c r="AL63" s="45"/>
     </row>
     <row r="64" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C64" s="60" t="s">
+      <c r="C64" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
-      <c r="L64" s="48"/>
-      <c r="M64" s="48"/>
-      <c r="N64" s="48"/>
-      <c r="O64" s="48"/>
-      <c r="P64" s="48"/>
-      <c r="Q64" s="48"/>
-      <c r="R64" s="48"/>
-      <c r="S64" s="48"/>
-      <c r="T64" s="48"/>
-      <c r="U64" s="48"/>
-      <c r="V64" s="48"/>
-      <c r="W64" s="48"/>
-      <c r="X64" s="48"/>
-      <c r="Y64" s="48"/>
-      <c r="Z64" s="48"/>
-      <c r="AA64" s="48"/>
-      <c r="AB64" s="48"/>
-      <c r="AC64" s="48"/>
-      <c r="AD64" s="48"/>
-      <c r="AE64" s="48"/>
-      <c r="AF64" s="48"/>
-      <c r="AG64" s="48"/>
-      <c r="AH64" s="48"/>
-      <c r="AI64" s="48"/>
-      <c r="AJ64" s="48"/>
-      <c r="AK64" s="48"/>
-      <c r="AL64" s="49"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="46"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="46"/>
+      <c r="O64" s="46"/>
+      <c r="P64" s="46"/>
+      <c r="Q64" s="46"/>
+      <c r="R64" s="46"/>
+      <c r="S64" s="46"/>
+      <c r="T64" s="46"/>
+      <c r="U64" s="46"/>
+      <c r="V64" s="46"/>
+      <c r="W64" s="46"/>
+      <c r="X64" s="46"/>
+      <c r="Y64" s="46"/>
+      <c r="Z64" s="46"/>
+      <c r="AA64" s="46"/>
+      <c r="AB64" s="46"/>
+      <c r="AC64" s="46"/>
+      <c r="AD64" s="46"/>
+      <c r="AE64" s="46"/>
+      <c r="AF64" s="46"/>
+      <c r="AG64" s="46"/>
+      <c r="AH64" s="46"/>
+      <c r="AI64" s="46"/>
+      <c r="AJ64" s="46"/>
+      <c r="AK64" s="46"/>
+      <c r="AL64" s="47"/>
     </row>
     <row r="65" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-      <c r="L65" s="46"/>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="46"/>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="46"/>
-      <c r="S65" s="46"/>
-      <c r="T65" s="46"/>
-      <c r="U65" s="46"/>
-      <c r="V65" s="46"/>
-      <c r="W65" s="46"/>
-      <c r="X65" s="46"/>
-      <c r="Y65" s="46"/>
-      <c r="Z65" s="46"/>
-      <c r="AA65" s="46"/>
-      <c r="AB65" s="46"/>
-      <c r="AC65" s="46"/>
-      <c r="AD65" s="46"/>
-      <c r="AE65" s="46"/>
-      <c r="AF65" s="46"/>
-      <c r="AG65" s="46"/>
-      <c r="AH65" s="46"/>
-      <c r="AI65" s="46"/>
-      <c r="AJ65" s="46"/>
-      <c r="AK65" s="46"/>
-      <c r="AL65" s="46"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+      <c r="L65" s="44"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="P65" s="44"/>
+      <c r="Q65" s="44"/>
+      <c r="R65" s="44"/>
+      <c r="S65" s="44"/>
+      <c r="T65" s="44"/>
+      <c r="U65" s="44"/>
+      <c r="V65" s="44"/>
+      <c r="W65" s="44"/>
+      <c r="X65" s="44"/>
+      <c r="Y65" s="44"/>
+      <c r="Z65" s="44"/>
+      <c r="AA65" s="44"/>
+      <c r="AB65" s="44"/>
+      <c r="AC65" s="44"/>
+      <c r="AD65" s="44"/>
+      <c r="AE65" s="44"/>
+      <c r="AF65" s="44"/>
+      <c r="AG65" s="44"/>
+      <c r="AH65" s="44"/>
+      <c r="AI65" s="44"/>
+      <c r="AJ65" s="44"/>
+      <c r="AK65" s="44"/>
+      <c r="AL65" s="44"/>
     </row>
     <row r="66" spans="3:38" ht="11.25" customHeight="1">
       <c r="C66" s="2"/>
       <c r="D66" s="3"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="33"/>
-      <c r="M66" s="33"/>
-      <c r="N66" s="33"/>
-      <c r="O66" s="33"/>
-      <c r="P66" s="33"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+      <c r="N66" s="31"/>
+      <c r="O66" s="31"/>
+      <c r="P66" s="31"/>
       <c r="Q66" s="3"/>
-      <c r="R66" s="33"/>
-      <c r="S66" s="33"/>
-      <c r="T66" s="33"/>
-      <c r="U66" s="33"/>
-      <c r="V66" s="33"/>
-      <c r="W66" s="33"/>
-      <c r="X66" s="33"/>
-      <c r="Y66" s="33"/>
-      <c r="Z66" s="33"/>
-      <c r="AA66" s="33"/>
-      <c r="AB66" s="33"/>
-      <c r="AC66" s="33"/>
-      <c r="AD66" s="33"/>
-      <c r="AE66" s="33"/>
+      <c r="R66" s="31"/>
+      <c r="S66" s="31"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="31"/>
+      <c r="V66" s="31"/>
+      <c r="W66" s="31"/>
+      <c r="X66" s="31"/>
+      <c r="Y66" s="31"/>
+      <c r="Z66" s="31"/>
+      <c r="AA66" s="31"/>
+      <c r="AB66" s="31"/>
+      <c r="AC66" s="31"/>
+      <c r="AD66" s="31"/>
+      <c r="AE66" s="31"/>
       <c r="AF66" s="2"/>
       <c r="AG66" s="2"/>
       <c r="AH66" s="2"/>
@@ -3770,33 +3816,33 @@
     <row r="67" spans="3:38" ht="11.1" customHeight="1">
       <c r="C67" s="2"/>
       <c r="D67" s="3"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="33"/>
-      <c r="M67" s="33"/>
-      <c r="N67" s="33"/>
-      <c r="O67" s="33"/>
-      <c r="P67" s="33"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
       <c r="Q67" s="3"/>
-      <c r="R67" s="33"/>
-      <c r="S67" s="33"/>
-      <c r="T67" s="33"/>
-      <c r="U67" s="33"/>
-      <c r="V67" s="33"/>
-      <c r="W67" s="33"/>
-      <c r="X67" s="33"/>
-      <c r="Y67" s="33"/>
-      <c r="Z67" s="33"/>
-      <c r="AA67" s="33"/>
-      <c r="AB67" s="33"/>
-      <c r="AC67" s="33"/>
-      <c r="AD67" s="33"/>
-      <c r="AE67" s="33"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="31"/>
+      <c r="Y67" s="31"/>
+      <c r="Z67" s="31"/>
+      <c r="AA67" s="31"/>
+      <c r="AB67" s="31"/>
+      <c r="AC67" s="31"/>
+      <c r="AD67" s="31"/>
+      <c r="AE67" s="31"/>
       <c r="AF67" s="2"/>
       <c r="AG67" s="2"/>
       <c r="AH67" s="2"/>
@@ -3808,33 +3854,33 @@
     <row r="68" spans="3:38" ht="11.25" customHeight="1">
       <c r="C68" s="2"/>
       <c r="D68" s="3"/>
-      <c r="E68" s="33"/>
-      <c r="F68" s="33"/>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="33"/>
-      <c r="M68" s="33"/>
-      <c r="N68" s="33"/>
-      <c r="O68" s="33"/>
-      <c r="P68" s="33"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="31"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="31"/>
+      <c r="M68" s="31"/>
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
+      <c r="P68" s="31"/>
       <c r="Q68" s="3"/>
-      <c r="R68" s="33"/>
-      <c r="S68" s="33"/>
-      <c r="T68" s="33"/>
-      <c r="U68" s="33"/>
-      <c r="V68" s="33"/>
-      <c r="W68" s="33"/>
-      <c r="X68" s="33"/>
-      <c r="Y68" s="33"/>
-      <c r="Z68" s="33"/>
-      <c r="AA68" s="33"/>
-      <c r="AB68" s="33"/>
-      <c r="AC68" s="33"/>
-      <c r="AD68" s="33"/>
-      <c r="AE68" s="33"/>
+      <c r="R68" s="31"/>
+      <c r="S68" s="31"/>
+      <c r="T68" s="31"/>
+      <c r="U68" s="31"/>
+      <c r="V68" s="31"/>
+      <c r="W68" s="31"/>
+      <c r="X68" s="31"/>
+      <c r="Y68" s="31"/>
+      <c r="Z68" s="31"/>
+      <c r="AA68" s="31"/>
+      <c r="AB68" s="31"/>
+      <c r="AC68" s="31"/>
+      <c r="AD68" s="31"/>
+      <c r="AE68" s="31"/>
       <c r="AF68" s="2"/>
       <c r="AG68" s="2"/>
       <c r="AH68" s="2"/>
@@ -3846,33 +3892,33 @@
     <row r="69" spans="3:38" ht="11.25" customHeight="1">
       <c r="C69" s="2"/>
       <c r="D69" s="3"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
-      <c r="N69" s="33"/>
-      <c r="O69" s="33"/>
-      <c r="P69" s="33"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31"/>
       <c r="Q69" s="3"/>
-      <c r="R69" s="33"/>
-      <c r="S69" s="33"/>
-      <c r="T69" s="33"/>
-      <c r="U69" s="33"/>
-      <c r="V69" s="33"/>
-      <c r="W69" s="33"/>
-      <c r="X69" s="33"/>
-      <c r="Y69" s="33"/>
-      <c r="Z69" s="33"/>
-      <c r="AA69" s="33"/>
-      <c r="AB69" s="33"/>
-      <c r="AC69" s="33"/>
-      <c r="AD69" s="33"/>
-      <c r="AE69" s="33"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
+      <c r="X69" s="31"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
+      <c r="AC69" s="31"/>
+      <c r="AD69" s="31"/>
+      <c r="AE69" s="31"/>
       <c r="AF69" s="2"/>
       <c r="AG69" s="2"/>
       <c r="AH69" s="2"/>
@@ -3884,33 +3930,33 @@
     <row r="70" spans="3:38" ht="11.25" customHeight="1">
       <c r="C70" s="2"/>
       <c r="D70" s="3"/>
-      <c r="E70" s="33"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="33"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="33"/>
-      <c r="J70" s="33"/>
-      <c r="K70" s="33"/>
-      <c r="L70" s="33"/>
-      <c r="M70" s="33"/>
-      <c r="N70" s="33"/>
-      <c r="O70" s="33"/>
-      <c r="P70" s="33"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
       <c r="Q70" s="3"/>
-      <c r="R70" s="33"/>
-      <c r="S70" s="33"/>
-      <c r="T70" s="33"/>
-      <c r="U70" s="33"/>
-      <c r="V70" s="33"/>
-      <c r="W70" s="33"/>
-      <c r="X70" s="33"/>
-      <c r="Y70" s="33"/>
-      <c r="Z70" s="33"/>
-      <c r="AA70" s="33"/>
-      <c r="AB70" s="33"/>
-      <c r="AC70" s="33"/>
-      <c r="AD70" s="33"/>
-      <c r="AE70" s="33"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="31"/>
+      <c r="AA70" s="31"/>
+      <c r="AB70" s="31"/>
+      <c r="AC70" s="31"/>
+      <c r="AD70" s="31"/>
+      <c r="AE70" s="31"/>
       <c r="AF70" s="2"/>
       <c r="AG70" s="2"/>
       <c r="AH70" s="2"/>
@@ -3922,33 +3968,33 @@
     <row r="71" spans="3:38" ht="11.25" customHeight="1">
       <c r="C71" s="2"/>
       <c r="D71" s="3"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="31"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
+      <c r="M71" s="31"/>
+      <c r="N71" s="31"/>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31"/>
       <c r="Q71" s="3"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="33"/>
-      <c r="T71" s="33"/>
-      <c r="U71" s="33"/>
-      <c r="V71" s="33"/>
-      <c r="W71" s="33"/>
-      <c r="X71" s="33"/>
-      <c r="Y71" s="33"/>
-      <c r="Z71" s="33"/>
-      <c r="AA71" s="33"/>
-      <c r="AB71" s="33"/>
-      <c r="AC71" s="33"/>
-      <c r="AD71" s="33"/>
-      <c r="AE71" s="33"/>
+      <c r="R71" s="31"/>
+      <c r="S71" s="31"/>
+      <c r="T71" s="31"/>
+      <c r="U71" s="31"/>
+      <c r="V71" s="31"/>
+      <c r="W71" s="31"/>
+      <c r="X71" s="31"/>
+      <c r="Y71" s="31"/>
+      <c r="Z71" s="31"/>
+      <c r="AA71" s="31"/>
+      <c r="AB71" s="31"/>
+      <c r="AC71" s="31"/>
+      <c r="AD71" s="31"/>
+      <c r="AE71" s="31"/>
       <c r="AF71" s="2"/>
       <c r="AG71" s="2"/>
       <c r="AH71" s="2"/>
@@ -3960,33 +4006,33 @@
     <row r="72" spans="3:38" ht="11.25" customHeight="1">
       <c r="C72" s="2"/>
       <c r="D72" s="3"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
-      <c r="M72" s="33"/>
-      <c r="N72" s="33"/>
-      <c r="O72" s="33"/>
-      <c r="P72" s="33"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
       <c r="Q72" s="3"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="33"/>
-      <c r="T72" s="33"/>
-      <c r="U72" s="33"/>
-      <c r="V72" s="33"/>
-      <c r="W72" s="33"/>
-      <c r="X72" s="33"/>
-      <c r="Y72" s="33"/>
-      <c r="Z72" s="33"/>
-      <c r="AA72" s="33"/>
-      <c r="AB72" s="33"/>
-      <c r="AC72" s="33"/>
-      <c r="AD72" s="33"/>
-      <c r="AE72" s="33"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="31"/>
+      <c r="V72" s="31"/>
+      <c r="W72" s="31"/>
+      <c r="X72" s="31"/>
+      <c r="Y72" s="31"/>
+      <c r="Z72" s="31"/>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
+      <c r="AC72" s="31"/>
+      <c r="AD72" s="31"/>
+      <c r="AE72" s="31"/>
       <c r="AF72" s="2"/>
       <c r="AG72" s="2"/>
       <c r="AH72" s="2"/>
@@ -3999,33 +4045,33 @@
     <row r="74" spans="3:38" ht="11.25" customHeight="1">
       <c r="C74" s="2"/>
       <c r="D74" s="3"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="33"/>
-      <c r="M74" s="33"/>
-      <c r="N74" s="33"/>
-      <c r="O74" s="33"/>
-      <c r="P74" s="33"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
+      <c r="M74" s="31"/>
+      <c r="N74" s="31"/>
+      <c r="O74" s="31"/>
+      <c r="P74" s="31"/>
       <c r="Q74" s="3"/>
-      <c r="R74" s="33"/>
-      <c r="S74" s="33"/>
-      <c r="T74" s="33"/>
-      <c r="U74" s="33"/>
-      <c r="V74" s="33"/>
-      <c r="W74" s="33"/>
-      <c r="X74" s="33"/>
-      <c r="Y74" s="33"/>
-      <c r="Z74" s="33"/>
-      <c r="AA74" s="33"/>
-      <c r="AB74" s="33"/>
-      <c r="AC74" s="33"/>
-      <c r="AD74" s="33"/>
-      <c r="AE74" s="33"/>
+      <c r="R74" s="31"/>
+      <c r="S74" s="31"/>
+      <c r="T74" s="31"/>
+      <c r="U74" s="31"/>
+      <c r="V74" s="31"/>
+      <c r="W74" s="31"/>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
+      <c r="AA74" s="31"/>
+      <c r="AB74" s="31"/>
+      <c r="AC74" s="31"/>
+      <c r="AD74" s="31"/>
+      <c r="AE74" s="31"/>
       <c r="AF74" s="2"/>
       <c r="AG74" s="2"/>
       <c r="AH74" s="2"/>
@@ -4037,33 +4083,33 @@
     <row r="75" spans="3:38" ht="11.25" customHeight="1">
       <c r="C75" s="2"/>
       <c r="D75" s="3"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="33"/>
-      <c r="L75" s="33"/>
-      <c r="M75" s="33"/>
-      <c r="N75" s="33"/>
-      <c r="O75" s="33"/>
-      <c r="P75" s="33"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
+      <c r="J75" s="31"/>
+      <c r="K75" s="31"/>
+      <c r="L75" s="31"/>
+      <c r="M75" s="31"/>
+      <c r="N75" s="31"/>
+      <c r="O75" s="31"/>
+      <c r="P75" s="31"/>
       <c r="Q75" s="3"/>
-      <c r="R75" s="33"/>
-      <c r="S75" s="33"/>
-      <c r="T75" s="33"/>
-      <c r="U75" s="33"/>
-      <c r="V75" s="33"/>
-      <c r="W75" s="33"/>
-      <c r="X75" s="33"/>
-      <c r="Y75" s="33"/>
-      <c r="Z75" s="33"/>
-      <c r="AA75" s="33"/>
-      <c r="AB75" s="33"/>
-      <c r="AC75" s="33"/>
-      <c r="AD75" s="33"/>
-      <c r="AE75" s="33"/>
+      <c r="R75" s="31"/>
+      <c r="S75" s="31"/>
+      <c r="T75" s="31"/>
+      <c r="U75" s="31"/>
+      <c r="V75" s="31"/>
+      <c r="W75" s="31"/>
+      <c r="X75" s="31"/>
+      <c r="Y75" s="31"/>
+      <c r="Z75" s="31"/>
+      <c r="AA75" s="31"/>
+      <c r="AB75" s="31"/>
+      <c r="AC75" s="31"/>
+      <c r="AD75" s="31"/>
+      <c r="AE75" s="31"/>
       <c r="AF75" s="2"/>
       <c r="AG75" s="2"/>
       <c r="AH75" s="2"/>
@@ -4075,33 +4121,33 @@
     <row r="76" spans="3:38" ht="11.25" customHeight="1">
       <c r="C76" s="2"/>
       <c r="D76" s="3"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="33"/>
-      <c r="J76" s="33"/>
-      <c r="K76" s="33"/>
-      <c r="L76" s="33"/>
-      <c r="M76" s="33"/>
-      <c r="N76" s="33"/>
-      <c r="O76" s="33"/>
-      <c r="P76" s="33"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="31"/>
+      <c r="K76" s="31"/>
+      <c r="L76" s="31"/>
+      <c r="M76" s="31"/>
+      <c r="N76" s="31"/>
+      <c r="O76" s="31"/>
+      <c r="P76" s="31"/>
       <c r="Q76" s="3"/>
-      <c r="R76" s="33"/>
-      <c r="S76" s="33"/>
-      <c r="T76" s="33"/>
-      <c r="U76" s="33"/>
-      <c r="V76" s="33"/>
-      <c r="W76" s="33"/>
-      <c r="X76" s="33"/>
-      <c r="Y76" s="33"/>
-      <c r="Z76" s="33"/>
-      <c r="AA76" s="33"/>
-      <c r="AB76" s="33"/>
-      <c r="AC76" s="33"/>
-      <c r="AD76" s="33"/>
-      <c r="AE76" s="33"/>
+      <c r="R76" s="31"/>
+      <c r="S76" s="31"/>
+      <c r="T76" s="31"/>
+      <c r="U76" s="31"/>
+      <c r="V76" s="31"/>
+      <c r="W76" s="31"/>
+      <c r="X76" s="31"/>
+      <c r="Y76" s="31"/>
+      <c r="Z76" s="31"/>
+      <c r="AA76" s="31"/>
+      <c r="AB76" s="31"/>
+      <c r="AC76" s="31"/>
+      <c r="AD76" s="31"/>
+      <c r="AE76" s="31"/>
       <c r="AF76" s="2"/>
       <c r="AG76" s="2"/>
       <c r="AH76" s="2"/>
@@ -4113,33 +4159,33 @@
     <row r="77" spans="3:38" ht="11.25" customHeight="1">
       <c r="C77" s="2"/>
       <c r="D77" s="3"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="33"/>
-      <c r="K77" s="33"/>
-      <c r="L77" s="33"/>
-      <c r="M77" s="33"/>
-      <c r="N77" s="33"/>
-      <c r="O77" s="33"/>
-      <c r="P77" s="33"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="31"/>
+      <c r="K77" s="31"/>
+      <c r="L77" s="31"/>
+      <c r="M77" s="31"/>
+      <c r="N77" s="31"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
       <c r="Q77" s="3"/>
-      <c r="R77" s="33"/>
-      <c r="S77" s="33"/>
-      <c r="T77" s="33"/>
-      <c r="U77" s="33"/>
-      <c r="V77" s="33"/>
-      <c r="W77" s="33"/>
-      <c r="X77" s="33"/>
-      <c r="Y77" s="33"/>
-      <c r="Z77" s="33"/>
-      <c r="AA77" s="33"/>
-      <c r="AB77" s="33"/>
-      <c r="AC77" s="33"/>
-      <c r="AD77" s="33"/>
-      <c r="AE77" s="33"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="31"/>
+      <c r="T77" s="31"/>
+      <c r="U77" s="31"/>
+      <c r="V77" s="31"/>
+      <c r="W77" s="31"/>
+      <c r="X77" s="31"/>
+      <c r="Y77" s="31"/>
+      <c r="Z77" s="31"/>
+      <c r="AA77" s="31"/>
+      <c r="AB77" s="31"/>
+      <c r="AC77" s="31"/>
+      <c r="AD77" s="31"/>
+      <c r="AE77" s="31"/>
       <c r="AF77" s="2"/>
       <c r="AG77" s="2"/>
       <c r="AH77" s="2"/>
@@ -4151,33 +4197,33 @@
     <row r="78" spans="3:38" ht="11.25" customHeight="1">
       <c r="C78" s="2"/>
       <c r="D78" s="3"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="33"/>
-      <c r="J78" s="33"/>
-      <c r="K78" s="33"/>
-      <c r="L78" s="33"/>
-      <c r="M78" s="33"/>
-      <c r="N78" s="33"/>
-      <c r="O78" s="33"/>
-      <c r="P78" s="33"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="31"/>
+      <c r="K78" s="31"/>
+      <c r="L78" s="31"/>
+      <c r="M78" s="31"/>
+      <c r="N78" s="31"/>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
       <c r="Q78" s="3"/>
-      <c r="R78" s="33"/>
-      <c r="S78" s="33"/>
-      <c r="T78" s="33"/>
-      <c r="U78" s="33"/>
-      <c r="V78" s="33"/>
-      <c r="W78" s="33"/>
-      <c r="X78" s="33"/>
-      <c r="Y78" s="33"/>
-      <c r="Z78" s="33"/>
-      <c r="AA78" s="33"/>
-      <c r="AB78" s="33"/>
-      <c r="AC78" s="33"/>
-      <c r="AD78" s="33"/>
-      <c r="AE78" s="33"/>
+      <c r="R78" s="31"/>
+      <c r="S78" s="31"/>
+      <c r="T78" s="31"/>
+      <c r="U78" s="31"/>
+      <c r="V78" s="31"/>
+      <c r="W78" s="31"/>
+      <c r="X78" s="31"/>
+      <c r="Y78" s="31"/>
+      <c r="Z78" s="31"/>
+      <c r="AA78" s="31"/>
+      <c r="AB78" s="31"/>
+      <c r="AC78" s="31"/>
+      <c r="AD78" s="31"/>
+      <c r="AE78" s="31"/>
       <c r="AF78" s="2"/>
       <c r="AG78" s="2"/>
       <c r="AH78" s="2"/>
@@ -4189,33 +4235,33 @@
     <row r="79" spans="3:38" ht="11.25" customHeight="1">
       <c r="C79" s="2"/>
       <c r="D79" s="3"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="33"/>
-      <c r="J79" s="33"/>
-      <c r="K79" s="33"/>
-      <c r="L79" s="33"/>
-      <c r="M79" s="33"/>
-      <c r="N79" s="33"/>
-      <c r="O79" s="33"/>
-      <c r="P79" s="33"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="31"/>
+      <c r="K79" s="31"/>
+      <c r="L79" s="31"/>
+      <c r="M79" s="31"/>
+      <c r="N79" s="31"/>
+      <c r="O79" s="31"/>
+      <c r="P79" s="31"/>
       <c r="Q79" s="3"/>
-      <c r="R79" s="33"/>
-      <c r="S79" s="33"/>
-      <c r="T79" s="33"/>
-      <c r="U79" s="33"/>
-      <c r="V79" s="33"/>
-      <c r="W79" s="33"/>
-      <c r="X79" s="33"/>
-      <c r="Y79" s="33"/>
-      <c r="Z79" s="33"/>
-      <c r="AA79" s="33"/>
-      <c r="AB79" s="33"/>
-      <c r="AC79" s="33"/>
-      <c r="AD79" s="33"/>
-      <c r="AE79" s="33"/>
+      <c r="R79" s="31"/>
+      <c r="S79" s="31"/>
+      <c r="T79" s="31"/>
+      <c r="U79" s="31"/>
+      <c r="V79" s="31"/>
+      <c r="W79" s="31"/>
+      <c r="X79" s="31"/>
+      <c r="Y79" s="31"/>
+      <c r="Z79" s="31"/>
+      <c r="AA79" s="31"/>
+      <c r="AB79" s="31"/>
+      <c r="AC79" s="31"/>
+      <c r="AD79" s="31"/>
+      <c r="AE79" s="31"/>
       <c r="AF79" s="2"/>
       <c r="AG79" s="2"/>
       <c r="AH79" s="2"/>
@@ -4227,40 +4273,40 @@
     <row r="80" spans="3:38" ht="11.25" customHeight="1"/>
     <row r="81" spans="3:38" ht="11.25" customHeight="1">
       <c r="D81" s="11"/>
-      <c r="E81" s="76" t="s">
+      <c r="E81" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="F81" s="77"/>
-      <c r="G81" s="77"/>
-      <c r="H81" s="77"/>
-      <c r="I81" s="77"/>
-      <c r="J81" s="77"/>
-      <c r="K81" s="77"/>
-      <c r="L81" s="77"/>
-      <c r="M81" s="77"/>
-      <c r="N81" s="77"/>
-      <c r="O81" s="77"/>
-      <c r="P81" s="77"/>
-      <c r="Q81" s="77"/>
-      <c r="R81" s="77"/>
-      <c r="S81" s="77"/>
-      <c r="T81" s="77"/>
-      <c r="U81" s="77"/>
-      <c r="V81" s="77"/>
-      <c r="W81" s="77"/>
-      <c r="X81" s="77"/>
-      <c r="Y81" s="77"/>
-      <c r="Z81" s="77"/>
-      <c r="AA81" s="77"/>
-      <c r="AB81" s="77"/>
-      <c r="AC81" s="77"/>
-      <c r="AD81" s="77"/>
-      <c r="AE81" s="77"/>
-      <c r="AF81" s="77"/>
-      <c r="AG81" s="77"/>
-      <c r="AH81" s="77"/>
-      <c r="AI81" s="77"/>
-      <c r="AJ81" s="78"/>
+      <c r="F81" s="95"/>
+      <c r="G81" s="95"/>
+      <c r="H81" s="95"/>
+      <c r="I81" s="95"/>
+      <c r="J81" s="95"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="95"/>
+      <c r="M81" s="95"/>
+      <c r="N81" s="95"/>
+      <c r="O81" s="95"/>
+      <c r="P81" s="95"/>
+      <c r="Q81" s="95"/>
+      <c r="R81" s="95"/>
+      <c r="S81" s="95"/>
+      <c r="T81" s="95"/>
+      <c r="U81" s="95"/>
+      <c r="V81" s="95"/>
+      <c r="W81" s="95"/>
+      <c r="X81" s="95"/>
+      <c r="Y81" s="95"/>
+      <c r="Z81" s="95"/>
+      <c r="AA81" s="95"/>
+      <c r="AB81" s="95"/>
+      <c r="AC81" s="95"/>
+      <c r="AD81" s="95"/>
+      <c r="AE81" s="95"/>
+      <c r="AF81" s="95"/>
+      <c r="AG81" s="95"/>
+      <c r="AH81" s="95"/>
+      <c r="AI81" s="95"/>
+      <c r="AJ81" s="96"/>
       <c r="AK81" s="11"/>
       <c r="AL81" s="11"/>
     </row>
@@ -4302,92 +4348,92 @@
       <c r="AL82" s="12"/>
     </row>
     <row r="83" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C83" s="68" t="s">
+      <c r="C83" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="71"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
-      <c r="M83" s="71"/>
-      <c r="N83" s="71"/>
-      <c r="O83" s="71"/>
-      <c r="P83" s="71"/>
-      <c r="Q83" s="72"/>
-      <c r="R83" s="68" t="s">
+      <c r="D83" s="81"/>
+      <c r="E83" s="81"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="82"/>
+      <c r="H83" s="83"/>
+      <c r="I83" s="83"/>
+      <c r="J83" s="83"/>
+      <c r="K83" s="83"/>
+      <c r="L83" s="83"/>
+      <c r="M83" s="83"/>
+      <c r="N83" s="83"/>
+      <c r="O83" s="83"/>
+      <c r="P83" s="83"/>
+      <c r="Q83" s="84"/>
+      <c r="R83" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="S83" s="68"/>
-      <c r="T83" s="68"/>
-      <c r="U83" s="68"/>
-      <c r="V83" s="74"/>
-      <c r="W83" s="74"/>
-      <c r="X83" s="74"/>
-      <c r="Y83" s="74"/>
-      <c r="Z83" s="74"/>
-      <c r="AA83" s="74"/>
-      <c r="AB83" s="74"/>
-      <c r="AC83" s="74"/>
-      <c r="AD83" s="74"/>
-      <c r="AE83" s="74"/>
-      <c r="AF83" s="68" t="s">
+      <c r="S83" s="81"/>
+      <c r="T83" s="81"/>
+      <c r="U83" s="81"/>
+      <c r="V83" s="85"/>
+      <c r="W83" s="85"/>
+      <c r="X83" s="85"/>
+      <c r="Y83" s="85"/>
+      <c r="Z83" s="85"/>
+      <c r="AA83" s="85"/>
+      <c r="AB83" s="85"/>
+      <c r="AC83" s="85"/>
+      <c r="AD83" s="85"/>
+      <c r="AE83" s="85"/>
+      <c r="AF83" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AG83" s="68"/>
-      <c r="AH83" s="68"/>
-      <c r="AI83" s="73"/>
-      <c r="AJ83" s="73"/>
-      <c r="AK83" s="73"/>
-      <c r="AL83" s="73"/>
+      <c r="AG83" s="81"/>
+      <c r="AH83" s="81"/>
+      <c r="AI83" s="97"/>
+      <c r="AJ83" s="97"/>
+      <c r="AK83" s="97"/>
+      <c r="AL83" s="97"/>
     </row>
     <row r="84" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C84" s="68" t="s">
+      <c r="C84" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="70"/>
-      <c r="H84" s="71"/>
-      <c r="I84" s="71"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="71"/>
-      <c r="L84" s="71"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="71"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="71"/>
-      <c r="Q84" s="72"/>
-      <c r="R84" s="68" t="s">
+      <c r="D84" s="81"/>
+      <c r="E84" s="81"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="83"/>
+      <c r="I84" s="83"/>
+      <c r="J84" s="83"/>
+      <c r="K84" s="83"/>
+      <c r="L84" s="83"/>
+      <c r="M84" s="83"/>
+      <c r="N84" s="83"/>
+      <c r="O84" s="83"/>
+      <c r="P84" s="83"/>
+      <c r="Q84" s="84"/>
+      <c r="R84" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="S84" s="68"/>
-      <c r="T84" s="68"/>
-      <c r="U84" s="68"/>
-      <c r="V84" s="74"/>
-      <c r="W84" s="74"/>
-      <c r="X84" s="74"/>
-      <c r="Y84" s="74"/>
-      <c r="Z84" s="74"/>
-      <c r="AA84" s="74"/>
-      <c r="AB84" s="74"/>
-      <c r="AC84" s="74"/>
-      <c r="AD84" s="74"/>
-      <c r="AE84" s="74"/>
-      <c r="AF84" s="69" t="s">
+      <c r="S84" s="81"/>
+      <c r="T84" s="81"/>
+      <c r="U84" s="81"/>
+      <c r="V84" s="85"/>
+      <c r="W84" s="85"/>
+      <c r="X84" s="85"/>
+      <c r="Y84" s="85"/>
+      <c r="Z84" s="85"/>
+      <c r="AA84" s="85"/>
+      <c r="AB84" s="85"/>
+      <c r="AC84" s="85"/>
+      <c r="AD84" s="85"/>
+      <c r="AE84" s="85"/>
+      <c r="AF84" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="AG84" s="69"/>
-      <c r="AH84" s="69"/>
-      <c r="AI84" s="75"/>
-      <c r="AJ84" s="75"/>
-      <c r="AK84" s="75"/>
-      <c r="AL84" s="75"/>
+      <c r="AG84" s="86"/>
+      <c r="AH84" s="86"/>
+      <c r="AI84" s="65"/>
+      <c r="AJ84" s="65"/>
+      <c r="AK84" s="65"/>
+      <c r="AL84" s="65"/>
     </row>
     <row r="85" spans="3:38" ht="11.25" customHeight="1">
       <c r="D85" s="1"/>
@@ -4427,82 +4473,82 @@
       <c r="AL85" s="1"/>
     </row>
     <row r="86" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C86" s="93" t="s">
+      <c r="C86" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
-      <c r="F86" s="94"/>
-      <c r="G86" s="94"/>
-      <c r="H86" s="94"/>
-      <c r="I86" s="94"/>
-      <c r="J86" s="94"/>
-      <c r="K86" s="94"/>
-      <c r="L86" s="94"/>
-      <c r="M86" s="94"/>
-      <c r="N86" s="94"/>
-      <c r="O86" s="94"/>
-      <c r="P86" s="94"/>
-      <c r="Q86" s="94"/>
-      <c r="R86" s="94"/>
-      <c r="S86" s="94"/>
-      <c r="T86" s="94"/>
-      <c r="U86" s="94"/>
-      <c r="V86" s="94"/>
-      <c r="W86" s="94"/>
-      <c r="X86" s="94"/>
-      <c r="Y86" s="94"/>
-      <c r="Z86" s="94"/>
-      <c r="AA86" s="94"/>
-      <c r="AB86" s="94"/>
-      <c r="AC86" s="94"/>
-      <c r="AD86" s="94"/>
-      <c r="AE86" s="94"/>
-      <c r="AF86" s="94"/>
-      <c r="AG86" s="94"/>
-      <c r="AH86" s="94"/>
-      <c r="AI86" s="94"/>
-      <c r="AJ86" s="94"/>
-      <c r="AK86" s="94"/>
-      <c r="AL86" s="95"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
+      <c r="H86" s="67"/>
+      <c r="I86" s="67"/>
+      <c r="J86" s="67"/>
+      <c r="K86" s="67"/>
+      <c r="L86" s="67"/>
+      <c r="M86" s="67"/>
+      <c r="N86" s="67"/>
+      <c r="O86" s="67"/>
+      <c r="P86" s="67"/>
+      <c r="Q86" s="67"/>
+      <c r="R86" s="67"/>
+      <c r="S86" s="67"/>
+      <c r="T86" s="67"/>
+      <c r="U86" s="67"/>
+      <c r="V86" s="67"/>
+      <c r="W86" s="67"/>
+      <c r="X86" s="67"/>
+      <c r="Y86" s="67"/>
+      <c r="Z86" s="67"/>
+      <c r="AA86" s="67"/>
+      <c r="AB86" s="67"/>
+      <c r="AC86" s="67"/>
+      <c r="AD86" s="67"/>
+      <c r="AE86" s="67"/>
+      <c r="AF86" s="67"/>
+      <c r="AG86" s="67"/>
+      <c r="AH86" s="67"/>
+      <c r="AI86" s="67"/>
+      <c r="AJ86" s="67"/>
+      <c r="AK86" s="67"/>
+      <c r="AL86" s="68"/>
     </row>
     <row r="87" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C87" s="96"/>
-      <c r="D87" s="97"/>
-      <c r="E87" s="97"/>
-      <c r="F87" s="97"/>
-      <c r="G87" s="97"/>
-      <c r="H87" s="97"/>
-      <c r="I87" s="97"/>
-      <c r="J87" s="97"/>
-      <c r="K87" s="97"/>
-      <c r="L87" s="97"/>
-      <c r="M87" s="97"/>
-      <c r="N87" s="97"/>
-      <c r="O87" s="97"/>
-      <c r="P87" s="97"/>
-      <c r="Q87" s="97"/>
-      <c r="R87" s="97"/>
-      <c r="S87" s="97"/>
-      <c r="T87" s="97"/>
-      <c r="U87" s="97"/>
-      <c r="V87" s="97"/>
-      <c r="W87" s="97"/>
-      <c r="X87" s="97"/>
-      <c r="Y87" s="97"/>
-      <c r="Z87" s="97"/>
-      <c r="AA87" s="97"/>
-      <c r="AB87" s="97"/>
-      <c r="AC87" s="97"/>
-      <c r="AD87" s="97"/>
-      <c r="AE87" s="97"/>
-      <c r="AF87" s="97"/>
-      <c r="AG87" s="97"/>
-      <c r="AH87" s="97"/>
-      <c r="AI87" s="97"/>
-      <c r="AJ87" s="97"/>
-      <c r="AK87" s="97"/>
-      <c r="AL87" s="98"/>
+      <c r="C87" s="69"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
+      <c r="Q87" s="70"/>
+      <c r="R87" s="70"/>
+      <c r="S87" s="70"/>
+      <c r="T87" s="70"/>
+      <c r="U87" s="70"/>
+      <c r="V87" s="70"/>
+      <c r="W87" s="70"/>
+      <c r="X87" s="70"/>
+      <c r="Y87" s="70"/>
+      <c r="Z87" s="70"/>
+      <c r="AA87" s="70"/>
+      <c r="AB87" s="70"/>
+      <c r="AC87" s="70"/>
+      <c r="AD87" s="70"/>
+      <c r="AE87" s="70"/>
+      <c r="AF87" s="70"/>
+      <c r="AG87" s="70"/>
+      <c r="AH87" s="70"/>
+      <c r="AI87" s="70"/>
+      <c r="AJ87" s="70"/>
+      <c r="AK87" s="70"/>
+      <c r="AL87" s="71"/>
     </row>
     <row r="88" spans="3:38" ht="11.25" customHeight="1">
       <c r="C88" s="13"/>
@@ -4867,46 +4913,46 @@
       <c r="AL102" s="26"/>
     </row>
     <row r="103" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C103" s="99" t="s">
+      <c r="C103" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D103" s="100"/>
-      <c r="E103" s="100"/>
-      <c r="F103" s="100"/>
-      <c r="G103" s="100"/>
-      <c r="H103" s="100"/>
-      <c r="I103" s="100"/>
-      <c r="J103" s="100"/>
-      <c r="K103" s="100"/>
-      <c r="L103" s="100"/>
-      <c r="M103" s="100"/>
-      <c r="N103" s="100"/>
-      <c r="O103" s="100"/>
-      <c r="P103" s="100"/>
-      <c r="Q103" s="100"/>
-      <c r="R103" s="100"/>
-      <c r="S103" s="100"/>
-      <c r="T103" s="101"/>
-      <c r="U103" s="102" t="s">
+      <c r="D103" s="73"/>
+      <c r="E103" s="73"/>
+      <c r="F103" s="73"/>
+      <c r="G103" s="73"/>
+      <c r="H103" s="73"/>
+      <c r="I103" s="73"/>
+      <c r="J103" s="73"/>
+      <c r="K103" s="73"/>
+      <c r="L103" s="73"/>
+      <c r="M103" s="73"/>
+      <c r="N103" s="73"/>
+      <c r="O103" s="73"/>
+      <c r="P103" s="73"/>
+      <c r="Q103" s="73"/>
+      <c r="R103" s="73"/>
+      <c r="S103" s="73"/>
+      <c r="T103" s="74"/>
+      <c r="U103" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="V103" s="103"/>
-      <c r="W103" s="103"/>
-      <c r="X103" s="103"/>
-      <c r="Y103" s="103"/>
-      <c r="Z103" s="103"/>
-      <c r="AA103" s="103"/>
-      <c r="AB103" s="103"/>
-      <c r="AC103" s="103"/>
-      <c r="AD103" s="103"/>
-      <c r="AE103" s="103"/>
-      <c r="AF103" s="103"/>
-      <c r="AG103" s="103"/>
-      <c r="AH103" s="103"/>
-      <c r="AI103" s="103"/>
-      <c r="AJ103" s="103"/>
-      <c r="AK103" s="103"/>
-      <c r="AL103" s="104"/>
+      <c r="V103" s="76"/>
+      <c r="W103" s="76"/>
+      <c r="X103" s="76"/>
+      <c r="Y103" s="76"/>
+      <c r="Z103" s="76"/>
+      <c r="AA103" s="76"/>
+      <c r="AB103" s="76"/>
+      <c r="AC103" s="76"/>
+      <c r="AD103" s="76"/>
+      <c r="AE103" s="76"/>
+      <c r="AF103" s="76"/>
+      <c r="AG103" s="76"/>
+      <c r="AH103" s="76"/>
+      <c r="AI103" s="76"/>
+      <c r="AJ103" s="76"/>
+      <c r="AK103" s="76"/>
+      <c r="AL103" s="77"/>
     </row>
     <row r="104" spans="3:38" ht="11.25" customHeight="1">
       <c r="C104" s="13"/>
@@ -5271,46 +5317,46 @@
       <c r="AL118" s="26"/>
     </row>
     <row r="119" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C119" s="105" t="s">
+      <c r="C119" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="D119" s="106"/>
-      <c r="E119" s="106"/>
-      <c r="F119" s="106"/>
-      <c r="G119" s="106"/>
-      <c r="H119" s="106"/>
-      <c r="I119" s="106"/>
-      <c r="J119" s="106"/>
-      <c r="K119" s="106"/>
-      <c r="L119" s="106"/>
-      <c r="M119" s="106"/>
-      <c r="N119" s="106"/>
-      <c r="O119" s="106"/>
-      <c r="P119" s="106"/>
-      <c r="Q119" s="106"/>
-      <c r="R119" s="106"/>
-      <c r="S119" s="106"/>
-      <c r="T119" s="107"/>
-      <c r="U119" s="105" t="s">
+      <c r="D119" s="79"/>
+      <c r="E119" s="79"/>
+      <c r="F119" s="79"/>
+      <c r="G119" s="79"/>
+      <c r="H119" s="79"/>
+      <c r="I119" s="79"/>
+      <c r="J119" s="79"/>
+      <c r="K119" s="79"/>
+      <c r="L119" s="79"/>
+      <c r="M119" s="79"/>
+      <c r="N119" s="79"/>
+      <c r="O119" s="79"/>
+      <c r="P119" s="79"/>
+      <c r="Q119" s="79"/>
+      <c r="R119" s="79"/>
+      <c r="S119" s="79"/>
+      <c r="T119" s="80"/>
+      <c r="U119" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="V119" s="106"/>
-      <c r="W119" s="106"/>
-      <c r="X119" s="106"/>
-      <c r="Y119" s="106"/>
-      <c r="Z119" s="106"/>
-      <c r="AA119" s="106"/>
-      <c r="AB119" s="106"/>
-      <c r="AC119" s="106"/>
-      <c r="AD119" s="106"/>
-      <c r="AE119" s="106"/>
-      <c r="AF119" s="106"/>
-      <c r="AG119" s="106"/>
-      <c r="AH119" s="106"/>
-      <c r="AI119" s="106"/>
-      <c r="AJ119" s="106"/>
-      <c r="AK119" s="106"/>
-      <c r="AL119" s="107"/>
+      <c r="V119" s="79"/>
+      <c r="W119" s="79"/>
+      <c r="X119" s="79"/>
+      <c r="Y119" s="79"/>
+      <c r="Z119" s="79"/>
+      <c r="AA119" s="79"/>
+      <c r="AB119" s="79"/>
+      <c r="AC119" s="79"/>
+      <c r="AD119" s="79"/>
+      <c r="AE119" s="79"/>
+      <c r="AF119" s="79"/>
+      <c r="AG119" s="79"/>
+      <c r="AH119" s="79"/>
+      <c r="AI119" s="79"/>
+      <c r="AJ119" s="79"/>
+      <c r="AK119" s="79"/>
+      <c r="AL119" s="80"/>
     </row>
     <row r="120" spans="3:38" ht="11.25" customHeight="1">
       <c r="C120" s="13"/>
@@ -5467,46 +5513,46 @@
       <c r="AL134" s="23"/>
     </row>
     <row r="135" spans="3:38" ht="11.25" customHeight="1">
-      <c r="C135" s="87" t="s">
+      <c r="C135" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D135" s="88"/>
-      <c r="E135" s="88"/>
-      <c r="F135" s="88"/>
-      <c r="G135" s="88"/>
-      <c r="H135" s="88"/>
-      <c r="I135" s="88"/>
-      <c r="J135" s="88"/>
-      <c r="K135" s="88"/>
-      <c r="L135" s="88"/>
-      <c r="M135" s="88"/>
-      <c r="N135" s="88"/>
-      <c r="O135" s="88"/>
-      <c r="P135" s="88"/>
-      <c r="Q135" s="88"/>
-      <c r="R135" s="88"/>
-      <c r="S135" s="88"/>
-      <c r="T135" s="89"/>
-      <c r="U135" s="90" t="s">
+      <c r="D135" s="60"/>
+      <c r="E135" s="60"/>
+      <c r="F135" s="60"/>
+      <c r="G135" s="60"/>
+      <c r="H135" s="60"/>
+      <c r="I135" s="60"/>
+      <c r="J135" s="60"/>
+      <c r="K135" s="60"/>
+      <c r="L135" s="60"/>
+      <c r="M135" s="60"/>
+      <c r="N135" s="60"/>
+      <c r="O135" s="60"/>
+      <c r="P135" s="60"/>
+      <c r="Q135" s="60"/>
+      <c r="R135" s="60"/>
+      <c r="S135" s="60"/>
+      <c r="T135" s="61"/>
+      <c r="U135" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V135" s="91"/>
-      <c r="W135" s="91"/>
-      <c r="X135" s="91"/>
-      <c r="Y135" s="91"/>
-      <c r="Z135" s="91"/>
-      <c r="AA135" s="91"/>
-      <c r="AB135" s="91"/>
-      <c r="AC135" s="91"/>
-      <c r="AD135" s="91"/>
-      <c r="AE135" s="91"/>
-      <c r="AF135" s="91"/>
-      <c r="AG135" s="91"/>
-      <c r="AH135" s="91"/>
-      <c r="AI135" s="91"/>
-      <c r="AJ135" s="91"/>
-      <c r="AK135" s="91"/>
-      <c r="AL135" s="92"/>
+      <c r="V135" s="63"/>
+      <c r="W135" s="63"/>
+      <c r="X135" s="63"/>
+      <c r="Y135" s="63"/>
+      <c r="Z135" s="63"/>
+      <c r="AA135" s="63"/>
+      <c r="AB135" s="63"/>
+      <c r="AC135" s="63"/>
+      <c r="AD135" s="63"/>
+      <c r="AE135" s="63"/>
+      <c r="AF135" s="63"/>
+      <c r="AG135" s="63"/>
+      <c r="AH135" s="63"/>
+      <c r="AI135" s="63"/>
+      <c r="AJ135" s="63"/>
+      <c r="AK135" s="63"/>
+      <c r="AL135" s="64"/>
     </row>
     <row r="136" spans="3:38" ht="11.25" customHeight="1"/>
     <row r="137" spans="3:38" ht="11.25" customHeight="1"/>
@@ -5549,10 +5595,10 @@
     <row r="174" spans="4:4" ht="11.25" customHeight="1"/>
     <row r="175" spans="4:4" ht="11.25" customHeight="1"/>
     <row r="176" spans="4:4" ht="11.25" customHeight="1">
-      <c r="D176" s="31"/>
+      <c r="D176" s="30"/>
     </row>
     <row r="177" spans="4:19" ht="11.25" customHeight="1">
-      <c r="D177" s="31"/>
+      <c r="D177" s="30"/>
     </row>
     <row r="178" spans="4:19" ht="11.25" customHeight="1">
       <c r="D178" s="29"/>
@@ -5612,6 +5658,40 @@
     <row r="206" ht="11.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="AC2:AM2"/>
+    <mergeCell ref="AC3:AM3"/>
+    <mergeCell ref="AC4:AM4"/>
+    <mergeCell ref="AC5:AM5"/>
+    <mergeCell ref="AC6:AM6"/>
+    <mergeCell ref="E9:AJ9"/>
+    <mergeCell ref="AF11:AH11"/>
+    <mergeCell ref="AF12:AH12"/>
+    <mergeCell ref="G11:Q11"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="G12:Q12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="V11:AE11"/>
+    <mergeCell ref="V12:AE12"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="E81:AJ81"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="G83:Q83"/>
+    <mergeCell ref="R83:U83"/>
+    <mergeCell ref="V83:AE83"/>
+    <mergeCell ref="AF83:AH83"/>
+    <mergeCell ref="AI83:AL83"/>
+    <mergeCell ref="C14:T14"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="C27:AL27"/>
+    <mergeCell ref="U14:AL14"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="G21:K21"/>
     <mergeCell ref="C135:T135"/>
     <mergeCell ref="U135:AL135"/>
     <mergeCell ref="AI84:AL84"/>
@@ -5625,40 +5705,6 @@
     <mergeCell ref="R84:U84"/>
     <mergeCell ref="V84:AE84"/>
     <mergeCell ref="AF84:AH84"/>
-    <mergeCell ref="C14:T14"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="C27:AL27"/>
-    <mergeCell ref="U14:AL14"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="E81:AJ81"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="G83:Q83"/>
-    <mergeCell ref="R83:U83"/>
-    <mergeCell ref="V83:AE83"/>
-    <mergeCell ref="AF83:AH83"/>
-    <mergeCell ref="AI83:AL83"/>
-    <mergeCell ref="E9:AJ9"/>
-    <mergeCell ref="AF11:AH11"/>
-    <mergeCell ref="AF12:AH12"/>
-    <mergeCell ref="G11:Q11"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="G12:Q12"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="V11:AE11"/>
-    <mergeCell ref="V12:AE12"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="AC2:AM2"/>
-    <mergeCell ref="AC3:AM3"/>
-    <mergeCell ref="AC4:AM4"/>
-    <mergeCell ref="AC5:AM5"/>
-    <mergeCell ref="AC6:AM6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
